--- a/chemical_db.xlsx
+++ b/chemical_db.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HM\Desktop\수질프로그램\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84FDC0A-D1D2-4350-A1CC-4EA38A975571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F67DFC7-8122-4304-B96C-821CD106D0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="304">
   <si>
     <t>System</t>
   </si>
@@ -105,36 +105,18 @@
     <t>Zinc / High Phosphate / High Polymer</t>
   </si>
   <si>
-    <t>강력한 방식, 저경도 수질 추천</t>
-  </si>
-  <si>
     <t>[pH 관리] pH 8.3 이상 상승 시 아연(Zinc) 스케일 발생 위험 👉 산 주입으로 pH 7.8~8.0 유지 필수</t>
   </si>
   <si>
     <t>MCO-308AA</t>
   </si>
   <si>
-    <t>High Phosphate / Polymer / Azole</t>
-  </si>
-  <si>
-    <t>고농도 인산염+아졸(동부식 방지)+폴리머 함유</t>
-  </si>
-  <si>
     <t>[고농축 운전] LSI +2.8 초과(예: +3.0) 시 단독 사용 위험 👉 분산제 추가 투입 및 황산 병행 주입 검토</t>
   </si>
   <si>
     <t>MCO-308E</t>
   </si>
   <si>
-    <t>냉각수 주처리제 (Basic)</t>
-  </si>
-  <si>
-    <t>High Phosphate / High Phosphonate</t>
-  </si>
-  <si>
-    <t>경제형 고농도 인산염 제품</t>
-  </si>
-  <si>
     <t>[스케일 주의] 폴리머 미포함 제품 👉 LSI +2.5 이상 상승 시 반드시 분산제 별도 병행 투입 필요</t>
   </si>
   <si>
@@ -156,21 +138,12 @@
     <t>High Phosphate / Polymer</t>
   </si>
   <si>
-    <t>[유속 관리] 유속이 느린 구간(0.5m/s 이하) 슬러지 침적 주의 👉 사이드 스트림 여과기 가동 권장</t>
-  </si>
-  <si>
     <t>MCO-4405</t>
   </si>
   <si>
-    <t>Zinc / Phosphate / High Polymer / High Phosphonate</t>
-  </si>
-  <si>
     <t>강력한 방식, 슬러지 분산 탁월</t>
   </si>
   <si>
-    <t>[아연 관리] 고알칼리 수질에서 Zinc Solubility 저하 주의 👉 pH 8.2 이하 관리 권장</t>
-  </si>
-  <si>
     <t>MCO-524AA</t>
   </si>
   <si>
@@ -180,21 +153,12 @@
     <t>강력한 방식, 고농도 인산염</t>
   </si>
   <si>
-    <t>[LSI 관리] LSI +2.8 이상 고부하 운전 시 👉 황산 주입 설비 가동 상태 점검 필수</t>
-  </si>
-  <si>
     <t>MCO-524+NA</t>
   </si>
   <si>
     <t>Zinc / High Phosphate / High Polymer / High Phosphonate</t>
   </si>
   <si>
-    <t>강력한 방식, 고농도 인산염, 스케일 제어</t>
-  </si>
-  <si>
-    <t>[정량 펌프] 점도가 있는 제품이므로 겨울철 배관 막힘 및 가스 잠김(Gas Binding) 수시 확인</t>
-  </si>
-  <si>
     <t>MCO-524SF</t>
   </si>
   <si>
@@ -204,9 +168,6 @@
     <t>고농도 인산염, 슬러지 분산 탁월</t>
   </si>
   <si>
-    <t>[Silica] 실리카 농도가 150ppm 이상일 경우 이 제품 단독으로는 한계 👉 HRD 계열 스케일 방지제 검토</t>
-  </si>
-  <si>
     <t>MCO-524T</t>
   </si>
   <si>
@@ -669,9 +630,6 @@
     <t>[주의] RO 멤브레인 유입 전 반드시 환원제(SBS)로 제거 필수 (ORP &lt; 200mV)</t>
   </si>
   <si>
-    <t>Cleaning (Low pH)</t>
-  </si>
-  <si>
     <t>MRI-2023</t>
   </si>
   <si>
@@ -889,14 +847,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>유기물/Oil 분산제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유기오염 및 oil Leak시 적용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>poly(ethylene-propylene)Glycol butoxy/Poly Dimethylsiolxane</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -921,11 +871,175 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>높은 인산칼슘 프로그램 적용시 추가 사용 권장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>높은 농축도 및 Ca 농도 500ppm이상 유지시 추가 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Acid Cleaning </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>높은 인산칼슘(T-PO4: 15~20ppm) 프로그램 적용시 추가 사용 권장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유기물/Oil 분산제(비이온성 계면활성제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유기오염 및 oil Leak시 적용/거품이 많이 발생하므로 필요시 소포제 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밀폐계 부식방지제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:19ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Organic Phosphate / Polymer / Azole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.0 ~ +1.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Organic Phosphate </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉각수 주처리제(CTBDR)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PBTC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 유기인산(100ppm 투입시 T-PO4: 8.4ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.5 ~ +2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP/PBTC/Polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체류시간이 길고, 농축배수가 높은 냉각시스템 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc / HEDP / High Polymer / sulfamic Acid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two 유기 인산염(100ppm 투입시 T-PO4: 4.7ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two 유기 인산염+아졸(동부식 방지)+폴리머 함유(100ppm 투입시 T-PO4: 4.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[아연 관리] 고알칼리 수질에서 Zinc Solubility 저하 주의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>👉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> pH 8.3~8.5 이하 관리 권장</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비아연계 인산염(100ppm 투입시 T-PO4: 20.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc / 정인산 / HEDP / Azole/ polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-유기인산염계 부식 및 스케일방지제(100ppm 투입시 T-PO4: 4.4ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 6.9ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[LSI 관리] LSI +2.5 이상 고부하 운전 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>👉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 황산 주입 설비 가동 상태 점검 필수</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc / 정인산 / HEDP / polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 13.7ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCO-524AA 제품의 2배함량(Azole 없음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정인산/고농도polymer/황산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+0.5 ~ +2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산주입형 고농도 인산염 부식방지제(100ppm 투입시 T-PO4: 6.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대형플랜트 및 고경도 수질에 적합</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -933,7 +1047,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -961,6 +1075,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1035,7 +1155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1054,6 +1174,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1362,12 +1485,12 @@
   <cols>
     <col min="2" max="2" width="17.4140625" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="32.75" customWidth="1"/>
-    <col min="5" max="5" width="13.08203125" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" customWidth="1"/>
     <col min="6" max="6" width="16.08203125" customWidth="1"/>
     <col min="7" max="7" width="14.1640625" customWidth="1"/>
-    <col min="8" max="8" width="47.08203125" customWidth="1"/>
-    <col min="9" max="9" width="34.75" customWidth="1"/>
+    <col min="8" max="8" width="43.08203125" customWidth="1"/>
+    <col min="9" max="9" width="60.4140625" customWidth="1"/>
     <col min="10" max="10" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1430,17 +1553,17 @@
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>126</v>
+      <c r="G2" s="7" t="s">
+        <v>280</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1451,7 +1574,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="21.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1459,10 +1582,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -1471,16 +1594,16 @@
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>26</v>
+        <v>279</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>27</v>
+        <v>290</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1499,10 +1622,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
@@ -1511,16 +1634,16 @@
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>31</v>
+        <v>281</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1539,7 +1662,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
@@ -1551,16 +1674,16 @@
         <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>35</v>
+        <v>283</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>36</v>
+        <v>284</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -1579,28 +1702,28 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>129</v>
+      <c r="G6" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>39</v>
+        <v>286</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>40</v>
+        <v>287</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1619,7 +1742,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>20</v>
@@ -1631,16 +1754,16 @@
         <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>42</v>
+        <v>288</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>43</v>
+        <v>294</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>291</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1659,7 +1782,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>20</v>
@@ -1671,16 +1794,16 @@
         <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>46</v>
+        <v>293</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>47</v>
+        <v>295</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>296</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1699,7 +1822,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>20</v>
@@ -1711,16 +1834,16 @@
         <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>50</v>
+        <v>297</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>51</v>
+        <v>298</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>52</v>
+        <v>299</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -1739,7 +1862,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>20</v>
@@ -1750,17 +1873,17 @@
       <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>129</v>
+      <c r="G10" s="7" t="s">
+        <v>301</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>54</v>
+        <v>300</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>55</v>
+        <v>302</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>56</v>
+        <v>303</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1779,7 +1902,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>20</v>
@@ -1791,16 +1914,16 @@
         <v>7</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1819,7 +1942,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>20</v>
@@ -1831,16 +1954,16 @@
         <v>7</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -1859,7 +1982,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>20</v>
@@ -1871,16 +1994,16 @@
         <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -1899,7 +2022,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>20</v>
@@ -1911,16 +2034,16 @@
         <v>7</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -1939,7 +2062,7 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>20</v>
@@ -1951,16 +2074,16 @@
         <v>7</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -1979,7 +2102,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>20</v>
@@ -1991,16 +2114,16 @@
         <v>7</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -2019,7 +2142,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>20</v>
@@ -2031,16 +2154,16 @@
         <v>7</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -2059,10 +2182,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E18" s="2">
         <v>100</v>
@@ -2071,16 +2194,16 @@
         <v>7</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -2099,7 +2222,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>20</v>
@@ -2111,16 +2234,16 @@
         <v>7</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -2139,10 +2262,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>20</v>
+        <v>277</v>
       </c>
       <c r="E20" s="2">
         <v>100</v>
@@ -2151,16 +2274,16 @@
         <v>7</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -2179,7 +2302,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>20</v>
@@ -2191,16 +2314,16 @@
         <v>7</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -2219,7 +2342,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>20</v>
@@ -2231,16 +2354,16 @@
         <v>7</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -2259,7 +2382,7 @@
         <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>20</v>
@@ -2271,16 +2394,16 @@
         <v>7</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -2299,7 +2422,7 @@
         <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>20</v>
@@ -2311,16 +2434,16 @@
         <v>7</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -2339,7 +2462,7 @@
         <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>20</v>
@@ -2351,16 +2474,16 @@
         <v>7</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
@@ -2379,10 +2502,10 @@
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="E26" s="2">
         <v>50</v>
@@ -2392,13 +2515,13 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -2417,10 +2540,10 @@
         <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E27" s="2">
         <v>50</v>
@@ -2432,13 +2555,13 @@
         <v>21</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
@@ -2457,10 +2580,10 @@
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E28" s="2">
         <v>30</v>
@@ -2472,13 +2595,13 @@
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -2497,10 +2620,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E29" s="2">
         <v>30</v>
@@ -2512,13 +2635,13 @@
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -2537,10 +2660,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E30" s="2">
         <v>50</v>
@@ -2552,13 +2675,13 @@
         <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -2577,10 +2700,10 @@
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2">
         <v>50</v>
@@ -2592,13 +2715,13 @@
         <v>21</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
@@ -2617,10 +2740,10 @@
         <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E32" s="2">
         <v>50</v>
@@ -2632,13 +2755,13 @@
         <v>21</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
@@ -2657,10 +2780,10 @@
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="E33" s="2">
         <v>50</v>
@@ -2672,13 +2795,13 @@
         <v>21</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
@@ -2697,10 +2820,10 @@
         <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E34" s="2">
         <v>30</v>
@@ -2712,13 +2835,13 @@
         <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
@@ -2737,10 +2860,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E35" s="2">
         <v>30</v>
@@ -2752,13 +2875,13 @@
         <v>21</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -2777,10 +2900,10 @@
         <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E36" s="2">
         <v>30</v>
@@ -2792,13 +2915,13 @@
         <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -2817,10 +2940,10 @@
         <v>8</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E37" s="2">
         <v>30</v>
@@ -2832,13 +2955,13 @@
         <v>21</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="I37" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J37" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
@@ -2857,10 +2980,10 @@
         <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E38" s="2">
         <v>50</v>
@@ -2872,13 +2995,13 @@
         <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -2897,10 +3020,10 @@
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E39" s="2">
         <v>50</v>
@@ -2912,13 +3035,13 @@
         <v>21</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
@@ -2937,10 +3060,10 @@
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E40" s="2">
         <v>30</v>
@@ -2952,13 +3075,13 @@
         <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -2977,10 +3100,10 @@
         <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E41" s="2">
         <v>30</v>
@@ -2992,13 +3115,13 @@
         <v>21</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -3017,10 +3140,10 @@
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E42" s="2">
         <v>50</v>
@@ -3032,13 +3155,13 @@
         <v>21</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
@@ -3057,10 +3180,10 @@
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E43" s="2">
         <v>50</v>
@@ -3072,13 +3195,13 @@
         <v>21</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
@@ -3097,10 +3220,10 @@
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E44" s="2">
         <v>40</v>
@@ -3112,13 +3235,13 @@
         <v>21</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
@@ -3137,10 +3260,10 @@
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E45" s="2">
         <v>40</v>
@@ -3152,13 +3275,13 @@
         <v>21</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
@@ -3177,10 +3300,10 @@
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E46" s="2">
         <v>40</v>
@@ -3192,13 +3315,13 @@
         <v>21</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
@@ -3217,10 +3340,10 @@
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E47" s="2">
         <v>40</v>
@@ -3232,13 +3355,13 @@
         <v>21</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
@@ -3257,10 +3380,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E48" s="2">
         <v>40</v>
@@ -3272,13 +3395,13 @@
         <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I48" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="J48" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
@@ -3297,10 +3420,10 @@
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E49" s="2">
         <v>40</v>
@@ -3312,13 +3435,13 @@
         <v>21</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
@@ -3337,10 +3460,10 @@
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E50" s="2">
         <v>40</v>
@@ -3352,13 +3475,13 @@
         <v>21</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
@@ -3377,10 +3500,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E51" s="2">
         <v>40</v>
@@ -3392,13 +3515,13 @@
         <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
@@ -3417,10 +3540,10 @@
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E52" s="2">
         <v>40</v>
@@ -3432,13 +3555,13 @@
         <v>21</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
@@ -3457,10 +3580,10 @@
         <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E53" s="2">
         <v>30</v>
@@ -3472,13 +3595,13 @@
         <v>21</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
@@ -3497,10 +3620,10 @@
         <v>13</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E54" s="2">
         <v>30</v>
@@ -3512,13 +3635,13 @@
         <v>21</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
@@ -3537,10 +3660,10 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E55" s="2">
         <v>30</v>
@@ -3552,13 +3675,13 @@
         <v>21</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
@@ -3577,10 +3700,10 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E56" s="2">
         <v>30</v>
@@ -3592,13 +3715,13 @@
         <v>21</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
@@ -3617,10 +3740,10 @@
         <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E57" s="2">
         <v>50</v>
@@ -3632,13 +3755,13 @@
         <v>21</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
@@ -3654,31 +3777,31 @@
         <v>14</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="E58" s="2">
         <v>50</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
@@ -3686,36 +3809,36 @@
       <c r="N58" s="2"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:18" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A59" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E59" s="2">
         <v>0</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
@@ -3723,36 +3846,36 @@
       <c r="N59" s="2"/>
       <c r="O59" s="1"/>
     </row>
-    <row r="60" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A60" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E60" s="2">
         <v>0</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
@@ -3760,36 +3883,36 @@
       <c r="N60" s="2"/>
       <c r="O60" s="1"/>
     </row>
-    <row r="61" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:18" ht="23.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A61" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E61" s="2">
         <v>0</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
@@ -3797,36 +3920,36 @@
       <c r="N61" s="2"/>
       <c r="O61" s="1"/>
     </row>
-    <row r="62" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:18" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A62" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E62" s="2">
         <v>0</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
@@ -3839,31 +3962,31 @@
         <v>14</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="E63" s="2">
         <v>0</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
@@ -3876,31 +3999,31 @@
         <v>14</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
@@ -3913,31 +4036,31 @@
         <v>14</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
@@ -3950,31 +4073,31 @@
         <v>14</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
@@ -3987,31 +4110,31 @@
         <v>14</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
@@ -4024,31 +4147,31 @@
         <v>14</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
@@ -4061,31 +4184,31 @@
         <v>14</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
@@ -4098,31 +4221,31 @@
         <v>14</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
@@ -4135,31 +4258,31 @@
         <v>14</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
@@ -4172,31 +4295,31 @@
         <v>14</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>

--- a/chemical_db.xlsx
+++ b/chemical_db.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HM\Desktop\수질프로그램\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F67DFC7-8122-4304-B96C-821CD106D0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF477BB-0D54-4B47-9C7D-18FA7650D77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="311">
   <si>
     <t>System</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Zinc / High Phosphate / High Polymer</t>
   </si>
   <si>
-    <t>[pH 관리] pH 8.3 이상 상승 시 아연(Zinc) 스케일 발생 위험 👉 산 주입으로 pH 7.8~8.0 유지 필수</t>
-  </si>
-  <si>
     <t>MCO-308AA</t>
   </si>
   <si>
@@ -123,156 +120,63 @@
     <t>MCO-308PB</t>
   </si>
   <si>
-    <t>High Phosphate</t>
-  </si>
-  <si>
-    <t>고농도 인산염(방식 우수)</t>
-  </si>
-  <si>
     <t>[칼슘 경도] 칼슘 경도가 500ppm 이상일 경우 인산칼슘 스케일 주의 👉 주기적 블로우다운 실시</t>
   </si>
   <si>
     <t>MCO-180E</t>
   </si>
   <si>
-    <t>High Phosphate / Polymer</t>
-  </si>
-  <si>
     <t>MCO-4405</t>
   </si>
   <si>
-    <t>강력한 방식, 슬러지 분산 탁월</t>
-  </si>
-  <si>
     <t>MCO-524AA</t>
   </si>
   <si>
-    <t>Zinc / High Phosphate / High Polymer / Phosphonate</t>
-  </si>
-  <si>
-    <t>강력한 방식, 고농도 인산염</t>
-  </si>
-  <si>
     <t>MCO-524+NA</t>
   </si>
   <si>
-    <t>Zinc / High Phosphate / High Polymer / High Phosphonate</t>
-  </si>
-  <si>
     <t>MCO-524SF</t>
   </si>
   <si>
-    <t>High Phosphate / High Polymer</t>
-  </si>
-  <si>
-    <t>고농도 인산염, 슬러지 분산 탁월</t>
-  </si>
-  <si>
     <t>MCO-524T</t>
   </si>
   <si>
-    <t>[수질 변동] 보급수 수질 변동(전도도 상승) 시 농축배수 하향 조정 선행</t>
-  </si>
-  <si>
     <t>MCO-524SAA</t>
   </si>
   <si>
-    <t>[고농축 운전] LSI +2.8 초과 시 👉 308AA와 동일하게 분산제 추가 및 산 주입 병행 필요</t>
-  </si>
-  <si>
     <t>MCO-1428P</t>
   </si>
   <si>
-    <t>Zinc / Phosphate / High Polymer</t>
-  </si>
-  <si>
-    <t>[저경도] 연수 사용 냉각탑에 최적화. 고경도수 유입 시 스케일 발생 우려</t>
-  </si>
-  <si>
     <t>MCO-8253A</t>
   </si>
   <si>
-    <t>Zinc / High Polymer</t>
-  </si>
-  <si>
-    <t>[부식 관리] 초기 투입 시 기초 피막 형성을 위해 평소 주입량의 2~3배 충격 투입 권장</t>
-  </si>
-  <si>
     <t>MCO-4832</t>
   </si>
   <si>
-    <t>Zinc / High Phosphate / Polymer / High Phosphonate</t>
-  </si>
-  <si>
-    <t>강력한 방식, 스케일 제어 강화</t>
-  </si>
-  <si>
-    <t>[LSI 관리] LSI +2.5~+2.8 구간 운전에 최적화된 제품</t>
-  </si>
-  <si>
     <t>MCO-4852</t>
   </si>
   <si>
-    <t>Zinc / High Phosphate / Phosphonate</t>
-  </si>
-  <si>
-    <t>강력한 방식 및 고농도 인산염</t>
-  </si>
-  <si>
-    <t>[분산제] 폴리머 함량이 낮으므로 슬라임 발생 시 분산제(MCD) 별도 투입 필수</t>
-  </si>
-  <si>
     <t>MCO-2021BAA</t>
   </si>
   <si>
-    <t>High Phosphate / High Polymer / Phosphonate</t>
-  </si>
-  <si>
-    <t>[pH 충격] 산 세정 직후 사용 시 pH가 급격히 오르지 않도록 주의 (인산칼슘 석출 위험)</t>
-  </si>
-  <si>
     <t>MCD-654</t>
   </si>
   <si>
     <t>고성능 분산제</t>
   </si>
   <si>
-    <t>Polymer / Surfactant</t>
-  </si>
-  <si>
-    <t>고성능 분산제 (슬라임/SS 제거)</t>
-  </si>
-  <si>
     <t>MCC-1828NA</t>
   </si>
   <si>
-    <t>[동절기] 기온 저하 시 제품 점도 상승 주의. 실내 보관 권장.</t>
-  </si>
-  <si>
     <t>MCC-370</t>
   </si>
   <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>복합 수처리제</t>
-  </si>
-  <si>
-    <t>[범용] 표준 수질(LSI +1.5~+2.0) 현장 전용. 고부하 운전 시 상위 제품 변경 필요.</t>
-  </si>
-  <si>
     <t>MCO-204-3</t>
   </si>
   <si>
-    <t>[철분] 유입수 내 철분(Fe) 농도가 높으면 인산철 스케일 발생 가능 👉 전처리 필요</t>
-  </si>
-  <si>
     <t>MCO-4882G</t>
   </si>
   <si>
-    <t>[LSI] LSI +2.5 이하 운전 권장. 그 이상은 산 주입 병행.</t>
-  </si>
-  <si>
     <t>MCO-120C</t>
   </si>
   <si>
@@ -288,27 +192,15 @@
     <t>Zinc</t>
   </si>
   <si>
-    <t>강력한 부식 억제</t>
-  </si>
-  <si>
-    <t>[방식 전용] 스케일 방지 기능 없음. 반드시 스케일 방지제와 혼합 사용 필요.</t>
-  </si>
-  <si>
     <t>MCD-747B</t>
   </si>
   <si>
     <t>MCD-4857D</t>
   </si>
   <si>
-    <t>[역세] 분산제 투입 후에는 여과기 부하가 걸리므로 역세 주기 단축 필요</t>
-  </si>
-  <si>
     <t>MCD-316</t>
   </si>
   <si>
-    <t>[오일] 열교환기 튜브에 기름(Oil) 성분이 유입되었을 때 유화 분산 효과 우수</t>
-  </si>
-  <si>
     <t>BioOX-781</t>
   </si>
   <si>
@@ -327,9 +219,6 @@
     <t>BioOx-240C</t>
   </si>
   <si>
-    <t>[pH] pH 8.5 이상의 고알칼리 수질에서는 반감기가 빨라지므로 증량 투입 필요.</t>
-  </si>
-  <si>
     <t>BioOX-244B</t>
   </si>
   <si>
@@ -339,42 +228,18 @@
     <t>산화성 살균제</t>
   </si>
   <si>
-    <t>Oxidizing</t>
-  </si>
-  <si>
-    <t>산화성 살균제 (레지오넬라 살균)</t>
-  </si>
-  <si>
-    <t>[부식] 과다 투입 시 배관 부식 유발 가능. 잔류염소 농도 0.5~1.0ppm 유지.</t>
-  </si>
-  <si>
     <t>MCD-4035</t>
   </si>
   <si>
-    <t>바이오 분산제</t>
-  </si>
-  <si>
-    <t>[바이오필름] 미생물 점액질(Slime) 제거 특화 제품. 레지오넬라 살균 보조 효과.</t>
-  </si>
-  <si>
     <t>MCD-403D1S</t>
   </si>
   <si>
     <t>MCD-403PT</t>
   </si>
   <si>
-    <t>[SS 제거] 냉각탑 하부 수조에 진흙(Mud) 퇴적 시 교반 후 투입하면 배출 효과 탁월</t>
-  </si>
-  <si>
     <t>MCD-1062</t>
   </si>
   <si>
-    <t>Phosphate / Phosphonate / Polymer</t>
-  </si>
-  <si>
-    <t>고성능 분산제: 슬라임 및 부유물질 침강 방지</t>
-  </si>
-  <si>
     <t>+0.5 ~ +2.0</t>
   </si>
   <si>
@@ -390,18 +255,9 @@
     <t>+0.5 ~ +1.5</t>
   </si>
   <si>
-    <t>냉각수 주처리제 (몰리브데이트)</t>
-  </si>
-  <si>
     <t>Zinc / Molybdate / Polymer</t>
   </si>
   <si>
-    <t>몰리브데이트 함유: 강력한 부식 억제 및 트레이서 기능</t>
-  </si>
-  <si>
-    <t>[몰리브데이트] Mo 농도 측정을 통해 약품 잔류량을 정확히 관리 가능 (부식 제어 탁월)</t>
-  </si>
-  <si>
     <t>DBNPA</t>
   </si>
   <si>
@@ -411,9 +267,6 @@
     <t>[Quick Kill] 투입 후 30분 내 빠른 살균 및 분해. 배출수 환경 영향 최소화.</t>
   </si>
   <si>
-    <t>[보호 세정] 방식제(Azole)와 스케일 억제제가 함유되어, 세정 중 배관 부식 방지 탁월</t>
-  </si>
-  <si>
     <t>MBO-CHZ-7</t>
   </si>
   <si>
@@ -429,12 +282,6 @@
     <t>MBO-1040</t>
   </si>
   <si>
-    <t>카보하이드라지드</t>
-  </si>
-  <si>
-    <t>강력한 고온용 탈산제 (인체 무해)</t>
-  </si>
-  <si>
     <t>[반응] 150℃ 이상 고온에서 산소 제거 반응 속도가 매우 빠름</t>
   </si>
   <si>
@@ -447,9 +294,6 @@
     <t>Neutralizing Amine</t>
   </si>
   <si>
-    <t>복수 배관 부식 방지 (pH 상승)</t>
-  </si>
-  <si>
     <t>[pH 관리] 응축수(복수) pH 8.5~9.0 유지되도록 주입량 조절 (CO2 중화)</t>
   </si>
   <si>
@@ -459,24 +303,9 @@
     <t>청관제 (복합)</t>
   </si>
   <si>
-    <t>Phosphate / Polymer / Sulfite</t>
-  </si>
-  <si>
-    <t>청관제+탈산제 올인원 (All-in-One)</t>
-  </si>
-  <si>
-    <t>[종합] 소형 관류보일러 전용. 약품 하나로 스케일/부식/용존산소 동시 제어.</t>
-  </si>
-  <si>
     <t>MBB-1100ODT/A</t>
   </si>
   <si>
-    <t>올인원 제품 (스케일/부식 방지)</t>
-  </si>
-  <si>
-    <t>[관리] 아황산 농도(20~40ppm)를 기준으로 주입량을 제어하세요.</t>
-  </si>
-  <si>
     <t>MBB-1123K2</t>
   </si>
   <si>
@@ -824,10 +653,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">저독성 복합 탈산제 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저독성 탈산 및 pH조정제(복합)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -863,14 +688,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Acrylic Polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인산칼슘 분산제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>높은 농축도 및 Ca 농도 500ppm이상 유지시 추가 적용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -879,10 +696,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>높은 인산칼슘(T-PO4: 15~20ppm) 프로그램 적용시 추가 사용 권장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>유기물/Oil 분산제(비이온성 계면활성제)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -895,10 +708,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:19ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Organic Phosphate / Polymer / Azole</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -931,19 +740,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>체류시간이 길고, 농축배수가 높은 냉각시스템 적용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Zinc / HEDP / High Polymer / sulfamic Acid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Two 유기 인산염(100ppm 투입시 T-PO4: 4.7ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Two 유기 인산염+아졸(동부식 방지)+폴리머 함유(100ppm 투입시 T-PO4: 4.6ppm)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -981,14 +782,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아연-유기인산염계 부식 및 스케일방지제(100ppm 투입시 T-PO4: 4.4ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 6.9ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">[LSI 관리] LSI +2.5 이상 고부하 운전 시 </t>
     </r>
@@ -1019,10 +812,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 13.7ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MCO-524AA 제품의 2배함량(Azole 없음)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1040,6 +829,343 @@
   </si>
   <si>
     <t>대형플랜트 및 고경도 수질에 적합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCO-524AA 제품의 1.3배함량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCO-524AA 제품의 1.8배함량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc / 정인산 / High Polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고경도 수질 및 농축배수 과부하 시스템 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:19ppm, Zn:2.2ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two 유기 인산염+Azole+폴리머 함유(100ppm 투입시 T-PO4: 4.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-유기인산염계 부식 및 스케일방지제(100ppm 투입시 T-PO4: 4.4ppm, Zn:1 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 6.9ppm,Zn:1 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 13.7ppm,Zn:2 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 8.8ppm,Zn:1.3 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 12.3ppm,Zn:1.8 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low Phosphate 방류기준(T-P, Zn)기준 제품(100ppm투입시 T-PO4:1.8ppm,Zn: 3ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-P 프로그램(100ppm 투입시 Zn:2.2ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Non-P 냉각수 프로그램 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>👉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> pH 8.3~8.5 이하 관리 권장</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc/ Azole/ High Polymer/sulfamic Acid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc/ 정인산 / HEDP / Polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:25.7ppm, Zn:2.2ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저농축 및 저경도 수질 추천(철강 플랜트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Zinc/ 정인산 / HEDP </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:19ppm, Zn:1.8ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저농축 및 저경도 수질 추천(철강 플랜트),직접수 계열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정인산/poly-phosphate/High polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 방식, 비아연계 인산염(100ppm 투입시 T-PO4:16ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몰리브데이트 함유: 강력한 부식 억제 (100ppm투입시 T-PO4:3.4ppm,Zn:1.4ppm,Mo:1.5ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉각수 저유속 및 하부부식 효과 탁월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-Po4: 5.4ppm, Zn: 4ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[아연 관리] 고알칼리 수질에서 Zinc Solubility 저하 주의 👉 pH 8.3~8.5 이하 관리 권장</t>
+  </si>
+  <si>
+    <t>Sodium Nitrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밀폐계 시스템 부식방지제(100ppm 투입시 NO2: 16ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부식성수질, 짧은 체류시간,Ca 500ppm이하 분산제 불필요, 폴리머 주입량: 0.5&lt;(UFPO4-FPO4)&lt;2.0ppm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체류시간이 길고, 농축배수가 높은 냉각시스템 적용,폴리머 주입량: 0.5&lt;(UFPO4-FPO4)&lt;2.0ppm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[pH 관리] pH 8.3 이상 상승 시 아연(Zinc) 스케일 발생 위험 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>👉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 산 주입으로 pH 7.8~8.0 유지 필수</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밀폐계 시스템(450~550ppm NO2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정인산/polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 인산염(방식 우수)(100ppm 투입시 T-PO4: 33ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저농축 및 인산염 단독 처리(비용절감)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정인산/SHM/polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 인산염, 철부식 탁월(100ppm 투입시 T-PO4:21.5ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철부식 산화물 및 저농축 시스템(철강 플랜트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유기인산염 단독(100ppm 투입시 T-PO4: 21ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴리인산염 단독(100ppm 투입시 T-PO4: 8.4ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 부식 억제(100ppm 투입시 T-Zn: 9.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[방식 전용] 냉각수 추가 부식 방지제. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polymer / 구연산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철분제거용 스케일분산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철강 분산제(OG분산제용)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HEDP/polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황산염(CaSO4, BaSO4) 스케일 억제 탁월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>농축기 시스템 특화 분산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Isothiazoline/질산동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안정화 액상 브롬계 살균제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NaBR/NaOCl/sulfamic Acis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>염소 살균제 pH 8이상 살균력 급감, pH 9수준까지도 살균력 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Polymer </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴리머 단독 제품(Ca염,철염,아연염)스케일 제거 탁월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성능 분산제 (CaCO3,CaPO4,Fe(OH)2,Zn(OH)2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성능 분산제 (CaCO3,CaPO4,Fe(OH)2,Zn(OH)3)</t>
+  </si>
+  <si>
+    <t>MCD-4035 50%제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성능 분산제 (CaCO3,CaPO4,Fe(OH)2,Zn(OH)4)</t>
+  </si>
+  <si>
+    <t>MCD-4035 50%제품, 안료 첨가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PBTC/ polymer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성능 분산제 (CaCO3,CaPO4,SiO2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실리카 전용 및 칼슘염 분산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈산소제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카보하이드라진 7% 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카보하이드라진 10% 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neutralizing Amine+ Carbohydrazide(8%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP/아황산나트륨/폴리머/DEHA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[종합] 소형,중형 수관보일러 전용. 약품 하나로 스케일/부식/용존산소 동시 제어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복합청관제(탈산소제+청관제+응축수부식방지제)(100ppm 투입시 T-PO4: 3.3ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복합청관제(탈산소제+청관제+응축수부식방지제)(100ppm 투입시 T-PO4: 6.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBB-1100ODT 50% 제품</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1047,7 +1173,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1081,6 +1207,12 @@
       <color theme="1"/>
       <name val="Segoe UI Emoji"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1166,6 +1298,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1174,9 +1309,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1489,8 +1621,8 @@
     <col min="5" max="5" width="9.1640625" customWidth="1"/>
     <col min="6" max="6" width="16.08203125" customWidth="1"/>
     <col min="7" max="7" width="14.1640625" customWidth="1"/>
-    <col min="8" max="8" width="43.08203125" customWidth="1"/>
-    <col min="9" max="9" width="60.4140625" customWidth="1"/>
+    <col min="8" max="8" width="39.4140625" customWidth="1"/>
+    <col min="9" max="9" width="66.6640625" customWidth="1"/>
     <col min="10" max="10" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1553,17 +1685,17 @@
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>280</v>
+      <c r="G2" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>268</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1574,7 +1706,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="21.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="30.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1582,10 +1714,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -1594,16 +1726,16 @@
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>279</v>
+        <v>217</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>290</v>
+        <v>242</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1622,10 +1754,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>282</v>
+        <v>220</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
@@ -1634,16 +1766,16 @@
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>289</v>
+        <v>226</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1662,7 +1794,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
@@ -1674,16 +1806,16 @@
         <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>283</v>
+        <v>221</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>284</v>
+        <v>222</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -1702,7 +1834,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>20</v>
@@ -1713,17 +1845,17 @@
       <c r="F6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>285</v>
+      <c r="G6" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>286</v>
+        <v>224</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>292</v>
+        <v>228</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1734,7 +1866,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:18" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1742,7 +1874,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>20</v>
@@ -1754,16 +1886,16 @@
         <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>288</v>
+        <v>225</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>291</v>
+        <v>227</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1782,7 +1914,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>20</v>
@@ -1794,16 +1926,16 @@
         <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>293</v>
+        <v>229</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>296</v>
+        <v>230</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1822,7 +1954,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>20</v>
@@ -1834,16 +1966,16 @@
         <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -1862,7 +1994,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>20</v>
@@ -1873,17 +2005,17 @@
       <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>301</v>
+      <c r="G10" s="4" t="s">
+        <v>234</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>303</v>
+        <v>236</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1902,7 +2034,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>20</v>
@@ -1914,16 +2046,16 @@
         <v>7</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>38</v>
+        <v>246</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>45</v>
+        <v>237</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1934,7 +2066,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1942,7 +2074,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>20</v>
@@ -1954,16 +2086,16 @@
         <v>7</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>40</v>
+        <v>229</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>38</v>
+        <v>247</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -1974,7 +2106,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1982,7 +2114,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>20</v>
@@ -1994,16 +2126,16 @@
         <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>49</v>
+        <v>239</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>35</v>
+        <v>248</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -2022,7 +2154,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>20</v>
@@ -2034,16 +2166,16 @@
         <v>7</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>52</v>
+        <v>251</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>53</v>
+        <v>250</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -2062,7 +2194,7 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>20</v>
@@ -2073,17 +2205,17 @@
       <c r="F15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>113</v>
+      <c r="G15" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>55</v>
+        <v>252</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>56</v>
+        <v>253</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>57</v>
+        <v>254</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -2102,7 +2234,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>20</v>
@@ -2114,16 +2246,16 @@
         <v>7</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>59</v>
+        <v>255</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>60</v>
+        <v>256</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -2142,7 +2274,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>20</v>
@@ -2154,16 +2286,16 @@
         <v>7</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>63</v>
+        <v>258</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>43</v>
+        <v>259</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>64</v>
+        <v>266</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -2182,10 +2314,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2">
         <v>100</v>
@@ -2194,16 +2326,16 @@
         <v>7</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>121</v>
+        <v>261</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -2222,7 +2354,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>20</v>
@@ -2234,16 +2366,16 @@
         <v>7</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>22</v>
+        <v>239</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>70</v>
+        <v>263</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -2262,10 +2394,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>277</v>
+        <v>216</v>
       </c>
       <c r="E20" s="2">
         <v>100</v>
@@ -2274,16 +2406,16 @@
         <v>7</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>72</v>
+        <v>264</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -2302,7 +2434,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>20</v>
@@ -2313,17 +2445,17 @@
       <c r="F21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>116</v>
+      <c r="G21" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>33</v>
+        <v>270</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>30</v>
+        <v>271</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>76</v>
+        <v>272</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -2342,7 +2474,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>20</v>
@@ -2354,16 +2486,16 @@
         <v>7</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>42</v>
+        <v>273</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>43</v>
+        <v>274</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -2382,7 +2514,7 @@
         <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>20</v>
@@ -2394,16 +2526,16 @@
         <v>7</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -2422,7 +2554,7 @@
         <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>20</v>
@@ -2434,16 +2566,16 @@
         <v>7</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>29</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>30</v>
+        <v>278</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -2462,7 +2594,7 @@
         <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>20</v>
@@ -2474,16 +2606,16 @@
         <v>7</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>85</v>
+        <v>281</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
@@ -2502,10 +2634,10 @@
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>264</v>
+        <v>206</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>265</v>
+        <v>207</v>
       </c>
       <c r="E26" s="2">
         <v>50</v>
@@ -2515,17 +2647,17 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="6"/>
+        <v>214</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="7"/>
       <c r="N26" s="2"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -2540,10 +2672,10 @@
         <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>267</v>
+        <v>209</v>
       </c>
       <c r="E27" s="2">
         <v>50</v>
@@ -2555,13 +2687,13 @@
         <v>21</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>268</v>
+        <v>210</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>269</v>
+        <v>211</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>272</v>
+        <v>212</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
@@ -2580,10 +2712,10 @@
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2">
         <v>30</v>
@@ -2595,13 +2727,13 @@
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>67</v>
+        <v>282</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>68</v>
+        <v>283</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>88</v>
+        <v>284</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -2620,10 +2752,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="E29" s="2">
         <v>30</v>
@@ -2635,13 +2767,13 @@
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>67</v>
+        <v>285</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>68</v>
+        <v>286</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>90</v>
+        <v>287</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -2660,10 +2792,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="E30" s="2">
         <v>50</v>
@@ -2675,13 +2807,13 @@
         <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>93</v>
+        <v>288</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -2700,10 +2832,10 @@
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="E31" s="2">
         <v>50</v>
@@ -2715,13 +2847,13 @@
         <v>21</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
@@ -2740,10 +2872,10 @@
         <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="E32" s="2">
         <v>50</v>
@@ -2755,13 +2887,13 @@
         <v>21</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
@@ -2780,10 +2912,10 @@
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2">
         <v>50</v>
@@ -2795,13 +2927,13 @@
         <v>21</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>102</v>
+        <v>289</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>103</v>
+        <v>291</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
@@ -2820,10 +2952,10 @@
         <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="E34" s="2">
         <v>30</v>
@@ -2835,13 +2967,13 @@
         <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>67</v>
+        <v>292</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>68</v>
+        <v>294</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
@@ -2860,10 +2992,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>267</v>
+        <v>209</v>
       </c>
       <c r="E35" s="2">
         <v>30</v>
@@ -2875,13 +3007,13 @@
         <v>21</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -2900,10 +3032,10 @@
         <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="E36" s="2">
         <v>30</v>
@@ -2915,13 +3047,13 @@
         <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>67</v>
+        <v>292</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>68</v>
+        <v>297</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>109</v>
+        <v>298</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -2940,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>66</v>
+        <v>209</v>
       </c>
       <c r="E37" s="2">
         <v>30</v>
@@ -2955,13 +3087,13 @@
         <v>21</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>111</v>
+        <v>299</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>112</v>
+        <v>300</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>125</v>
+        <v>301</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
@@ -2980,10 +3112,10 @@
         <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>127</v>
+        <v>302</v>
       </c>
       <c r="E38" s="2">
         <v>50</v>
@@ -2995,13 +3127,13 @@
         <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>260</v>
+        <v>303</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -3020,10 +3152,10 @@
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2">
         <v>50</v>
@@ -3035,13 +3167,13 @@
         <v>21</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>261</v>
+        <v>203</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>262</v>
+        <v>204</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
@@ -3060,10 +3192,10 @@
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>131</v>
+        <v>302</v>
       </c>
       <c r="E40" s="2">
         <v>30</v>
@@ -3075,13 +3207,13 @@
         <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>132</v>
+        <v>304</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -3100,10 +3232,10 @@
         <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2">
         <v>30</v>
@@ -3115,13 +3247,13 @@
         <v>21</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>136</v>
+        <v>305</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -3140,10 +3272,10 @@
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="E42" s="2">
         <v>50</v>
@@ -3155,13 +3287,13 @@
         <v>21</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>141</v>
+        <v>306</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>142</v>
+        <v>309</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
@@ -3180,10 +3312,10 @@
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="E43" s="2">
         <v>50</v>
@@ -3195,13 +3327,13 @@
         <v>21</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>141</v>
+        <v>306</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>145</v>
+        <v>308</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>146</v>
+        <v>310</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
@@ -3220,10 +3352,10 @@
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E44" s="2">
         <v>40</v>
@@ -3235,13 +3367,13 @@
         <v>21</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
@@ -3260,10 +3392,10 @@
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E45" s="2">
         <v>40</v>
@@ -3275,13 +3407,13 @@
         <v>21</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
@@ -3300,10 +3432,10 @@
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E46" s="2">
         <v>40</v>
@@ -3315,13 +3447,13 @@
         <v>21</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
@@ -3340,10 +3472,10 @@
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E47" s="2">
         <v>40</v>
@@ -3355,13 +3487,13 @@
         <v>21</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
@@ -3380,10 +3512,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E48" s="2">
         <v>40</v>
@@ -3395,13 +3527,13 @@
         <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
@@ -3420,10 +3552,10 @@
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E49" s="2">
         <v>40</v>
@@ -3435,13 +3567,13 @@
         <v>21</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>256</v>
+        <v>199</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
@@ -3460,10 +3592,10 @@
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E50" s="2">
         <v>40</v>
@@ -3475,13 +3607,13 @@
         <v>21</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
@@ -3500,10 +3632,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E51" s="2">
         <v>40</v>
@@ -3515,13 +3647,13 @@
         <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
@@ -3540,10 +3672,10 @@
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E52" s="2">
         <v>40</v>
@@ -3555,13 +3687,13 @@
         <v>21</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
@@ -3580,10 +3712,10 @@
         <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="E53" s="2">
         <v>30</v>
@@ -3595,13 +3727,13 @@
         <v>21</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
@@ -3620,10 +3752,10 @@
         <v>13</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E54" s="2">
         <v>30</v>
@@ -3635,13 +3767,13 @@
         <v>21</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
@@ -3660,10 +3792,10 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E55" s="2">
         <v>30</v>
@@ -3675,13 +3807,13 @@
         <v>21</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>186</v>
+        <v>129</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
@@ -3700,10 +3832,10 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E56" s="2">
         <v>30</v>
@@ -3715,13 +3847,13 @@
         <v>21</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
@@ -3740,10 +3872,10 @@
         <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="E57" s="2">
         <v>50</v>
@@ -3755,13 +3887,13 @@
         <v>21</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>255</v>
+        <v>198</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
@@ -3777,31 +3909,31 @@
         <v>14</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E58" s="2">
         <v>50</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>194</v>
+        <v>137</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>196</v>
+        <v>139</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
@@ -3814,31 +3946,31 @@
         <v>14</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>273</v>
+        <v>213</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>198</v>
+        <v>141</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="E59" s="2">
         <v>0</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>201</v>
+        <v>144</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
@@ -3851,31 +3983,31 @@
         <v>14</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>273</v>
+        <v>213</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>204</v>
+        <v>147</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="E60" s="2">
         <v>0</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
@@ -3888,31 +4020,31 @@
         <v>14</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>273</v>
+        <v>213</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>206</v>
+        <v>149</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="E61" s="2">
         <v>0</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
@@ -3925,31 +4057,31 @@
         <v>14</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>273</v>
+        <v>213</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>208</v>
+        <v>151</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="E62" s="2">
         <v>0</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
@@ -3962,31 +4094,31 @@
         <v>14</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>210</v>
+        <v>153</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>212</v>
+        <v>155</v>
       </c>
       <c r="E63" s="2">
         <v>0</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>213</v>
+        <v>156</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>214</v>
+        <v>157</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>215</v>
+        <v>158</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>216</v>
+        <v>159</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
@@ -3999,31 +4131,31 @@
         <v>14</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>217</v>
+        <v>160</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>218</v>
+        <v>161</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>222</v>
+        <v>165</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
@@ -4036,31 +4168,31 @@
         <v>14</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>227</v>
+        <v>170</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
@@ -4073,31 +4205,31 @@
         <v>14</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>227</v>
+        <v>170</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
@@ -4110,31 +4242,31 @@
         <v>14</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>227</v>
+        <v>170</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
@@ -4147,31 +4279,31 @@
         <v>14</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>232</v>
+        <v>175</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>233</v>
+        <v>176</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>236</v>
+        <v>179</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
@@ -4184,31 +4316,31 @@
         <v>14</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>242</v>
+        <v>185</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
@@ -4221,31 +4353,31 @@
         <v>14</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>243</v>
+        <v>186</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>244</v>
+        <v>187</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>245</v>
+        <v>188</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
@@ -4258,31 +4390,31 @@
         <v>14</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
@@ -4295,31 +4427,31 @@
         <v>14</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>

--- a/chemical_db.xlsx
+++ b/chemical_db.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HM\Desktop\수질프로그램\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF477BB-0D54-4B47-9C7D-18FA7650D77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE1727F-26BF-4741-A4F6-DAB3B97005C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="337">
   <si>
     <t>System</t>
   </si>
@@ -291,9 +291,6 @@
     <t>복수 처리제</t>
   </si>
   <si>
-    <t>Neutralizing Amine</t>
-  </si>
-  <si>
     <t>[pH 관리] 응축수(복수) pH 8.5~9.0 유지되도록 주입량 조절 (CO2 중화)</t>
   </si>
   <si>
@@ -312,129 +309,45 @@
     <t>청관제 (인산염)</t>
   </si>
   <si>
-    <t>Phosphate / Polymer</t>
-  </si>
-  <si>
-    <t>표준형 인산염계 청관제</t>
-  </si>
-  <si>
-    <t>[PO4] 보일러수 내 인산염 농도 20~40ppm 유지 관리</t>
-  </si>
-  <si>
     <t>MBB-1123C</t>
   </si>
   <si>
-    <t>스케일 분산력 강화 제품</t>
-  </si>
-  <si>
-    <t>[경도] 급수 경도 누출이 잦은 현장의 스케일 방지에 효과적</t>
-  </si>
-  <si>
     <t>MBB-1123CHY</t>
   </si>
   <si>
-    <t>고성능 인산염+폴리머 복합제</t>
-  </si>
-  <si>
-    <t>[분산] 칼슘/마그네슘 스케일 뿐만 아니라 실리카 분산 효과 우수</t>
-  </si>
-  <si>
     <t>MBB-1123CHM</t>
   </si>
   <si>
-    <t>다목적 보일러 청관제</t>
-  </si>
-  <si>
-    <t>[범용] 중저압 보일러의 표준 수처리 프로그램에 적합</t>
-  </si>
-  <si>
     <t>MBB-2217CHM</t>
   </si>
   <si>
-    <t>고농축 인산염 청관제</t>
-  </si>
-  <si>
-    <t>[경제성] 유효 성분 농도가 높아 적은 주입량으로도 효과 발휘</t>
-  </si>
-  <si>
     <t>MBB-2800</t>
   </si>
   <si>
-    <t>프리미엄 스케일 방지제</t>
-  </si>
-  <si>
-    <t>[철분] 급수 중 철분(Fe) 함량이 높을 때 슬러지 유동화 탁월</t>
-  </si>
-  <si>
     <t>MBB-2806</t>
   </si>
   <si>
-    <t>고성능 슬러지 분산제 함유</t>
-  </si>
-  <si>
-    <t>[블로우다운] 슬러지를 부드럽게 만들어 배출(Blowdown) 효율 증대</t>
-  </si>
-  <si>
     <t>MBB-3000</t>
   </si>
   <si>
-    <t>고압 보일러용 청관제</t>
-  </si>
-  <si>
-    <t>[고압] 압력 20kg/cm2 이상 보일러의 스케일 제어에 최적화</t>
-  </si>
-  <si>
     <t>MBB-3820</t>
   </si>
   <si>
-    <t>고부하 대응 청관제</t>
-  </si>
-  <si>
-    <t>[부하 변동] 증기 부하 변동이 심한 현장에서도 안정적인 수질 유지</t>
-  </si>
-  <si>
     <t>MBB-1123NP</t>
   </si>
   <si>
     <t>청관제 (Non-PO4)</t>
   </si>
   <si>
-    <t>Polymer / Chelant</t>
-  </si>
-  <si>
-    <t>인산염 없는(Non-PO4) 전폴리머 청관제</t>
-  </si>
-  <si>
-    <t>[Non-PO4] 인산철 스케일 생성 원천 차단. 인산염 규제 사업장 및 고압 보일러 추천.</t>
-  </si>
-  <si>
     <t>MBC-8790</t>
   </si>
   <si>
-    <t>고농축 복수 처리제</t>
-  </si>
-  <si>
-    <t>[거리] 증기 배관 길이가 긴 현장의 말단부 부식 방지에 효과적</t>
-  </si>
-  <si>
     <t>MBC-8763</t>
   </si>
   <si>
-    <t>식품첨가물급 성분 함유</t>
-  </si>
-  <si>
-    <t>[식품] 식품 공장 등 증기가 제품에 직접 닿는 공정에 사용 가능</t>
-  </si>
-  <si>
     <t>MBC-2020</t>
   </si>
   <si>
-    <t>표준형 복수 처리제</t>
-  </si>
-  <si>
-    <t>[방청] 증기/응축수 라인의 전반적인 부식(Red Water) 방지</t>
-  </si>
-  <si>
     <t>MBO-7010K</t>
   </si>
   <si>
@@ -450,15 +363,6 @@
     <t>ORP Check</t>
   </si>
   <si>
-    <t>Sulfamic acid / NaOH</t>
-  </si>
-  <si>
-    <t>염소계 살균제 (전처리용)</t>
-  </si>
-  <si>
-    <t>[주의] RO 멤브레인 유입 전 반드시 환원제(SBS)로 제거 필수 (ORP &lt; 200mV)</t>
-  </si>
-  <si>
     <t>MRI-2023</t>
   </si>
   <si>
@@ -468,36 +372,18 @@
     <t>pH 2~3</t>
   </si>
   <si>
-    <t>H3PO4 / H-40(HEDTA-3Na)</t>
-  </si>
-  <si>
     <t>무기물 스케일(CaCO3, Fe) 제거용 산성 세정제</t>
   </si>
   <si>
-    <t>[세정] 40℃ 순환 세정 시 세정 효율 극대화 (pH 상시 모니터링)</t>
-  </si>
-  <si>
     <t>MIC-2001</t>
   </si>
   <si>
-    <t>BORRESPERSE NA / Citric Acid</t>
-  </si>
-  <si>
     <t>MIC-2004</t>
   </si>
   <si>
-    <t>HPMA / Citric Acid</t>
-  </si>
-  <si>
     <t>MIC-2003</t>
   </si>
   <si>
-    <t>Citric Acid</t>
-  </si>
-  <si>
-    <t>Cleaning (High pH)</t>
-  </si>
-  <si>
     <t>MIC-26B</t>
   </si>
   <si>
@@ -516,9 +402,6 @@
     <t>[세정] 오일/슬라임 오염 시 계면활성제 효과로 세정력 우수</t>
   </si>
   <si>
-    <t>Antiscalant (High LSI)</t>
-  </si>
-  <si>
     <t>MRO-8844</t>
   </si>
   <si>
@@ -528,12 +411,6 @@
     <t>LSI &lt; +2.5</t>
   </si>
   <si>
-    <t>PBTC / EDTA-4Na</t>
-  </si>
-  <si>
-    <t>고경도/고온 대응 스케일 방지제</t>
-  </si>
-  <si>
     <t>[고경도] 칼슘 경도가 높은 난용성 수질에 적합</t>
   </si>
   <si>
@@ -546,9 +423,6 @@
     <t>LSI &lt; +2.3</t>
   </si>
   <si>
-    <t>ATMP / EDTA-4Na</t>
-  </si>
-  <si>
     <t>탄산칼슘(CaCO3) 제어 표준형</t>
   </si>
   <si>
@@ -561,57 +435,30 @@
     <t>MRO-2021</t>
   </si>
   <si>
-    <t>Antiscalant (Chelant)</t>
-  </si>
-  <si>
     <t>MRO-6730</t>
   </si>
   <si>
-    <t>LSI &lt; +2.0</t>
-  </si>
-  <si>
     <t>EDTA-4Na / T.E.A</t>
   </si>
   <si>
-    <t>금속 이온 봉쇄(Chelating) 효과</t>
-  </si>
-  <si>
-    <t>[금속] 철분/망간 등 금속 이온에 의한 멤브레인 폐색 방지</t>
-  </si>
-  <si>
     <t>Antiscalant (Sulfate)</t>
   </si>
   <si>
     <t>MRD-1500</t>
   </si>
   <si>
-    <t>DETPMP / HEDP</t>
-  </si>
-  <si>
     <t>황산염(CaSO4, BaSO4) 스케일 억제 탁월</t>
   </si>
   <si>
     <t>[지하수] 황산이온(SO4) 농도가 높은 지하수 원수에 최적</t>
   </si>
   <si>
-    <t>Antiscalant (Dispersant)</t>
-  </si>
-  <si>
     <t>MRD-2200AP</t>
   </si>
   <si>
     <t>LSI &lt; +2.8</t>
   </si>
   <si>
-    <t>ATMP / DETPMP</t>
-  </si>
-  <si>
-    <t>실리카/황산염 특화 분산제 (High Performance)</t>
-  </si>
-  <si>
-    <t>[고회수율] Silica 200ppm 이상 또는 LSI +2.8 고부하 운전 가능</t>
-  </si>
-  <si>
     <t>MRD-2200</t>
   </si>
   <si>
@@ -637,14 +484,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SHMP , NaOH (Na/PO4= 2.8:1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHMP , NaOH (Na/PO4= 3:1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>응축수 부식방지 및 방식제(휘발성)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -659,9 +498,6 @@
   <si>
     <t>[저압,중압] 저압,중압 보일러의 용존산소 제거 및 금속 부동태화 형성 탁월</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[고압] 고압 보일러의 용존산소 제거 및 금속 부동태화 형성 탁월</t>
   </si>
   <si>
     <t>MCD-738</t>
@@ -1166,6 +1002,321 @@
   </si>
   <si>
     <t>MBB-1100ODT 50% 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Alkaline Cleaning </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP/KOH/폴리머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순수용 및 고압(KOH) 보일러 청관제(100ppm 투입시 T-PO4: 9.1%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순수 수질 알칼리도 없어서 pH 상향조정하기 위해 알칼리도가 높은 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP/NaOH/폴리머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연수용 저압 보일러 청관제(100ppm 투입시 T-PO4: 5.0%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보일러 농축배수 10~15 Cycle 시스템 이용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP/KOH/Carbo/MEA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고압 및 농축배수 50배수 Cycle 시스템 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고압 보일러 청관제 및 응축수 부식방지제 (100ppm 투입시 T-PO4: 0.8ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고압 보일러 청관제 및 응축수 부식방지제 (100ppm 투입시 T-PO4: 2.4ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBB-1123CHY 3배 농도 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP/KOH/Carbo/MEA/폴리머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고압 보일러 청관제 및 응축수 강화 방지제 (100ppm 투입시 T-PO4: 4.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급수 수질 안정화 시스템+ 응축수 스팀 라인 보호에 초점/분산제가 없으므로 경도성분 유입시 스케일 유발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP , NaOH (Na/PO4= 2.8:1)/폴리머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP , NaOH (Na/PO4= 2.93:1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중,고압 보일러 청관제(100ppm 투입시 T-PO4:5.1ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중,고압 보일러 청관제(100ppm 투입시 T-PO4:6.1ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP , NaOH (Na/PO4= 2.84:1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Na/PO4 비율이 3.0보다 낮으므로, 물이 농축되어도 가성소다가 단독으로 생성안됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저압.중압(60kg/cm2 이하)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저압,중압 보일러 청관제(100ppm 투입시 T-PO4:5.1ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cabo./폴리머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐열보일러용 청관제 (Non-PO4) 청관제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐열 보일러용/Blow-down 어려운 시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저압 보일러 청관제(100ppm 투입시 T-PO4: 3.2ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Na/PO4 비율이 2.6~2.85 구간으로 안정화된 인산염 처리/전처리 경도성분 철저히 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP,가성소다/폴리머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저압용 보일러,농축배수 15배수 이상 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이클로 아민 + M.E.A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응축수 부식 방지제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응축수 배관 길이 초반부+말단부에 효과적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBC-8790제품의 1.5배 농도 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응축수 배관 길이 초반부 효과적/현장 길이가 긴 시스템에 효과 저하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복합 탈산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈산소제+ 응축수 부식방지제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고압,대형 보일러 시스템 적용(휘발성 처리 프로그램)/응축수 말단 pH 유의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BioOX-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산화성 살균제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ca(Ocl)2 70%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효염소 1ppm 투입시 Ca 및 M-알칼리도(as CaCo3기준) 약 0.7~0.8ppm 상승</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sulfamic acid / NaOH/NaOCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안정화된 염소 살균제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설파믹산 결합염소, 일반적인 RO 시스템 비추천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구연산/인산/글리코산/킬레이트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성능 무기 세정제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄산칼슘외 철분,망간,실리카등 난용성 오염물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구연산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구연산/분산제(소량)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구연산/스케일방지제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RO시스템 표준 세정제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄산칼슘(가성비 세정제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황산칼슘 및 실리카 제거 어려움</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[세정] 단순 산 세정제, 40℃ 순환 세정 시 세정 효율 극대화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PBTC / EDTA-4Na/TEA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH 10~12</t>
+  </si>
+  <si>
+    <t>pH 10~13</t>
+  </si>
+  <si>
+    <t>pH 10~14</t>
+  </si>
+  <si>
+    <t>pH 10~15</t>
+  </si>
+  <si>
+    <t>pH 10~16</t>
+  </si>
+  <si>
+    <t>유기물 오염</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 유기물 오염</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG/ EDTA-4Na/TEA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유기오염이 약한곳, 정기적인 RO CIP 약품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유기오염 및 Fe,Mn 오염도가 심한곳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유기오염 및 Fe,Mn 오염도가 매우 심한곳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경제형 알칼리세정제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오염이 심하지 않은 정기적 세정/비용절감</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATMP / DETPMP/HEDP/폴리머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATMP / DETPMP/HEDP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DETPMP / HEDP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄산칼슘(CaCO3) 및 황산염 스케일,콜로이드 입자 분산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[고회수율]  LSI +2.8 고부하 운전 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MRD-3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LSI &lt; +2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HEDP/A-5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄산칼슘외 실리카 전용 분산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실리카전용 분산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antiscalant (Silica)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1287,7 +1438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1299,6 +1450,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1612,7 +1766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="17.4140625" customWidth="1"/>
@@ -1686,16 +1840,16 @@
         <v>7</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>241</v>
+        <v>187</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1717,7 +1871,7 @@
         <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -1729,10 +1883,10 @@
         <v>69</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>217</v>
+        <v>163</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>24</v>
@@ -1757,7 +1911,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>220</v>
+        <v>166</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
@@ -1769,10 +1923,10 @@
         <v>70</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>226</v>
+        <v>172</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>26</v>
@@ -1809,10 +1963,10 @@
         <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>221</v>
+        <v>167</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>28</v>
@@ -1846,16 +2000,16 @@
         <v>7</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>224</v>
+        <v>170</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>267</v>
+        <v>213</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1889,13 +2043,13 @@
         <v>68</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>243</v>
+        <v>189</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1929,13 +2083,13 @@
         <v>68</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>244</v>
+        <v>190</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1969,13 +2123,13 @@
         <v>68</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -2006,16 +2160,16 @@
         <v>7</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>233</v>
+        <v>179</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>236</v>
+        <v>182</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -2049,13 +2203,13 @@
         <v>68</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -2089,13 +2243,13 @@
         <v>68</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>247</v>
+        <v>193</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -2129,13 +2283,13 @@
         <v>68</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>240</v>
+        <v>186</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -2169,13 +2323,13 @@
         <v>68</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>249</v>
+        <v>195</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>250</v>
+        <v>196</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -2206,16 +2360,16 @@
         <v>7</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>252</v>
+        <v>198</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>253</v>
+        <v>199</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -2249,13 +2403,13 @@
         <v>68</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -2289,13 +2443,13 @@
         <v>71</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>266</v>
+        <v>212</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -2332,10 +2486,10 @@
         <v>73</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>261</v>
+        <v>207</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -2369,13 +2523,13 @@
         <v>68</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>263</v>
+        <v>209</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -2397,7 +2551,7 @@
         <v>44</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="E20" s="2">
         <v>100</v>
@@ -2409,13 +2563,13 @@
         <v>72</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>269</v>
+        <v>215</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -2446,16 +2600,16 @@
         <v>7</v>
       </c>
       <c r="G21" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -2489,13 +2643,13 @@
         <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>273</v>
+        <v>219</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>275</v>
+        <v>221</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -2529,10 +2683,10 @@
         <v>72</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>276</v>
+        <v>222</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>48</v>
@@ -2569,10 +2723,10 @@
         <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>277</v>
+        <v>223</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>48</v>
@@ -2612,10 +2766,10 @@
         <v>51</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
@@ -2634,10 +2788,10 @@
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="E26" s="2">
         <v>50</v>
@@ -2647,17 +2801,17 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="7"/>
+        <v>160</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="8"/>
       <c r="N26" s="2"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -2675,7 +2829,7 @@
         <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="E27" s="2">
         <v>50</v>
@@ -2687,13 +2841,13 @@
         <v>21</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
@@ -2727,13 +2881,13 @@
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -2767,13 +2921,13 @@
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -2792,10 +2946,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>55</v>
+        <v>295</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>296</v>
       </c>
       <c r="E30" s="2">
         <v>50</v>
@@ -2807,13 +2961,13 @@
         <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>58</v>
+        <v>296</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>59</v>
+        <v>298</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -2832,7 +2986,7 @@
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>56</v>
@@ -2847,7 +3001,7 @@
         <v>21</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>57</v>
+        <v>234</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>58</v>
@@ -2872,7 +3026,7 @@
         <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>56</v>
@@ -2887,13 +3041,13 @@
         <v>21</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
@@ -2912,10 +3066,10 @@
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E33" s="2">
         <v>50</v>
@@ -2927,13 +3081,13 @@
         <v>21</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>290</v>
+        <v>74</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>291</v>
+        <v>76</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
@@ -2949,16 +3103,16 @@
         <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>209</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>7</v>
@@ -2967,13 +3121,13 @@
         <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>294</v>
+        <v>235</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>293</v>
+        <v>237</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
@@ -2992,10 +3146,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="E35" s="2">
         <v>30</v>
@@ -3007,13 +3161,13 @@
         <v>21</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>295</v>
+        <v>240</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -3032,10 +3186,10 @@
         <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="E36" s="2">
         <v>30</v>
@@ -3047,13 +3201,13 @@
         <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>298</v>
+        <v>242</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -3072,10 +3226,10 @@
         <v>8</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="E37" s="2">
         <v>30</v>
@@ -3087,13 +3241,13 @@
         <v>21</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
@@ -3106,34 +3260,34 @@
     </row>
     <row r="38" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>302</v>
+        <v>155</v>
       </c>
       <c r="E38" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -3152,10 +3306,10 @@
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="E39" s="2">
         <v>50</v>
@@ -3167,13 +3321,13 @@
         <v>21</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>197</v>
+        <v>144</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
@@ -3192,13 +3346,13 @@
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>302</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>10</v>
@@ -3207,13 +3361,13 @@
         <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>304</v>
+        <v>150</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -3229,31 +3383,31 @@
         <v>10</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>84</v>
+        <v>248</v>
       </c>
       <c r="E41" s="2">
         <v>30</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>305</v>
+        <v>145</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -3269,31 +3423,31 @@
         <v>10</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E42" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>307</v>
+        <v>85</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
@@ -3312,13 +3466,13 @@
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E43" s="2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -3327,13 +3481,13 @@
         <v>21</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>310</v>
+        <v>253</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
@@ -3352,13 +3506,13 @@
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E44" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
@@ -3367,13 +3521,13 @@
         <v>21</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>92</v>
+        <v>252</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>93</v>
+        <v>254</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
@@ -3392,13 +3546,13 @@
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E45" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
@@ -3407,13 +3561,13 @@
         <v>21</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>96</v>
+        <v>259</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
@@ -3432,13 +3586,13 @@
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E46" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
@@ -3447,13 +3601,13 @@
         <v>21</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>92</v>
+        <v>261</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>99</v>
+        <v>262</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>100</v>
+        <v>263</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
@@ -3472,13 +3626,13 @@
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E47" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -3487,13 +3641,13 @@
         <v>21</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>102</v>
+        <v>266</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>103</v>
+        <v>265</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
@@ -3512,13 +3666,13 @@
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E48" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -3527,13 +3681,13 @@
         <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>106</v>
+        <v>268</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
@@ -3552,13 +3706,13 @@
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
@@ -3567,13 +3721,13 @@
         <v>21</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
@@ -3592,13 +3746,13 @@
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E50" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
@@ -3607,13 +3761,13 @@
         <v>21</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>111</v>
+        <v>274</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>112</v>
+        <v>277</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
@@ -3632,13 +3786,13 @@
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E51" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -3647,13 +3801,13 @@
         <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>200</v>
+        <v>276</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>114</v>
+        <v>275</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>115</v>
+        <v>284</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
@@ -3672,13 +3826,13 @@
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E52" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -3687,13 +3841,13 @@
         <v>21</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>92</v>
+        <v>273</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>117</v>
+        <v>279</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>118</v>
+        <v>278</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
@@ -3712,13 +3866,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E53" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
@@ -3727,13 +3881,13 @@
         <v>21</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>122</v>
+        <v>283</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>123</v>
+        <v>286</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
@@ -3749,31 +3903,31 @@
         <v>10</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="E54" s="2">
         <v>30</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>125</v>
+        <v>281</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
@@ -3792,7 +3946,7 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>84</v>
@@ -3807,13 +3961,13 @@
         <v>21</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>128</v>
+        <v>288</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>129</v>
+        <v>289</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
@@ -3832,7 +3986,7 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>84</v>
@@ -3847,13 +4001,13 @@
         <v>21</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>131</v>
+        <v>288</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>132</v>
+        <v>290</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
@@ -3869,31 +4023,31 @@
         <v>10</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E57" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>198</v>
+        <v>287</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>201</v>
+        <v>288</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>205</v>
+        <v>291</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
@@ -3906,71 +4060,74 @@
     </row>
     <row r="58" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A58" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>63</v>
+        <v>292</v>
       </c>
       <c r="E58" s="2">
         <v>50</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>139</v>
+        <v>293</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>140</v>
+        <v>294</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="1"/>
-    </row>
-    <row r="59" spans="1:18" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+    </row>
+    <row r="59" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A59" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>213</v>
+        <v>105</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="E59" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>144</v>
+        <v>299</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>146</v>
+        <v>301</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
@@ -3983,31 +4140,31 @@
         <v>14</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E60" s="2">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="E60" s="5">
+        <v>0.05</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>148</v>
+        <v>302</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>145</v>
+        <v>303</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>146</v>
+        <v>304</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
@@ -4015,36 +4172,36 @@
       <c r="N60" s="2"/>
       <c r="O60" s="1"/>
     </row>
-    <row r="61" spans="1:18" ht="23.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A61" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E61" s="2">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="E61" s="5">
+        <v>0.05</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>150</v>
+        <v>306</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>145</v>
+        <v>309</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>146</v>
+        <v>310</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
@@ -4052,36 +4209,36 @@
       <c r="N61" s="2"/>
       <c r="O61" s="1"/>
     </row>
-    <row r="62" spans="1:18" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:18" ht="23.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A62" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E62" s="2">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="E62" s="5">
+        <v>0.05</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>152</v>
+        <v>307</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>146</v>
+        <v>308</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
@@ -4089,36 +4246,36 @@
       <c r="N62" s="2"/>
       <c r="O62" s="1"/>
     </row>
-    <row r="63" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:18" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A63" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E63" s="2">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="E63" s="5">
+        <v>0.05</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>157</v>
+        <v>305</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>158</v>
+        <v>309</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>159</v>
+        <v>311</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
@@ -4131,31 +4288,31 @@
         <v>14</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>160</v>
+        <v>257</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E64" s="2">
-        <v>5</v>
+        <v>117</v>
+      </c>
+      <c r="E64" s="5">
+        <v>0.05</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
@@ -4168,31 +4325,31 @@
         <v>14</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>167</v>
+        <v>257</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E65" s="2">
-        <v>5</v>
+        <v>117</v>
+      </c>
+      <c r="E65" s="5">
+        <v>0.05</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>169</v>
+        <v>313</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>171</v>
+        <v>318</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
@@ -4205,31 +4362,31 @@
         <v>14</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>167</v>
+        <v>257</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E66" s="2">
-        <v>5</v>
+        <v>117</v>
+      </c>
+      <c r="E66" s="5">
+        <v>0.05</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>169</v>
+        <v>314</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>171</v>
+        <v>318</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>172</v>
+        <v>321</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
@@ -4242,31 +4399,31 @@
         <v>14</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>167</v>
+        <v>257</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E67" s="2">
-        <v>5</v>
+        <v>117</v>
+      </c>
+      <c r="E67" s="5">
+        <v>0.05</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>169</v>
+        <v>315</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>170</v>
+        <v>320</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>171</v>
+        <v>319</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>172</v>
+        <v>322</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
@@ -4279,31 +4436,31 @@
         <v>14</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E68" s="2">
-        <v>5</v>
+        <v>117</v>
+      </c>
+      <c r="E68" s="5">
+        <v>0.05</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>177</v>
+        <v>316</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>178</v>
+        <v>320</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>179</v>
+        <v>319</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>180</v>
+        <v>323</v>
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
@@ -4316,31 +4473,31 @@
         <v>14</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>181</v>
+        <v>257</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E69" s="2">
-        <v>5</v>
+        <v>117</v>
+      </c>
+      <c r="E69" s="5">
+        <v>0.05</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>163</v>
+        <v>317</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>184</v>
+        <v>324</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>185</v>
+        <v>325</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
@@ -4348,36 +4505,36 @@
       <c r="N69" s="2"/>
       <c r="O69" s="1"/>
     </row>
-    <row r="70" spans="1:15" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A70" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>188</v>
+        <v>124</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>189</v>
+        <v>328</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
@@ -4385,36 +4542,36 @@
       <c r="N70" s="2"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:15" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A71" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>189</v>
+        <v>326</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>171</v>
+        <v>329</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>172</v>
+        <v>330</v>
       </c>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
@@ -4427,37 +4584,111 @@
         <v>14</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>194</v>
+        <v>327</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="1"/>
+    </row>
+    <row r="73" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E73" s="2">
+        <v>6</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="1"/>
+    </row>
+    <row r="74" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E74" s="2">
+        <v>5</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/chemical_db.xlsx
+++ b/chemical_db.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HM\Desktop\수질프로그램\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE1727F-26BF-4741-A4F6-DAB3B97005C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FFFFFD-F50F-4E2D-8BC9-D96A36943E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="353">
   <si>
     <t>System</t>
   </si>
@@ -1318,6 +1318,62 @@
   <si>
     <t>Antiscalant (Silica)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_LSI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_CaSO4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_SiO2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_BaSO4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_SrSO4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_CaF2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.5~30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200~400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.5~31</t>
+  </si>
+  <si>
+    <t>200~401</t>
+  </si>
+  <si>
+    <t>2.5~32</t>
+  </si>
+  <si>
+    <t>200~402</t>
+  </si>
+  <si>
+    <t>2.5~33</t>
+  </si>
+  <si>
+    <t>200~403</t>
+  </si>
+  <si>
+    <t>2.5~34</t>
+  </si>
+  <si>
+    <t>200~404</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1430,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1434,11 +1490,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1463,6 +1530,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1774,10 +1847,13 @@
     <col min="4" max="4" width="24.33203125" customWidth="1"/>
     <col min="5" max="5" width="9.1640625" customWidth="1"/>
     <col min="6" max="6" width="16.08203125" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
-    <col min="8" max="8" width="39.4140625" customWidth="1"/>
-    <col min="9" max="9" width="66.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="7" max="7" width="21.4140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="39.4140625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="24" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.25" customWidth="1"/>
+    <col min="14" max="14" width="11.08203125" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -1811,12 +1887,24 @@
       <c r="J1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>342</v>
+      </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
@@ -1851,9 +1939,9 @@
       <c r="J2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
       <c r="N2" s="2"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -1891,9 +1979,9 @@
       <c r="J3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
       <c r="N3" s="2"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -4320,7 +4408,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A65" s="2" t="s">
         <v>14</v>
       </c>
@@ -4357,7 +4445,7 @@
       <c r="N65" s="2"/>
       <c r="O65" s="1"/>
     </row>
-    <row r="66" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A66" s="2" t="s">
         <v>14</v>
       </c>
@@ -4394,7 +4482,7 @@
       <c r="N66" s="2"/>
       <c r="O66" s="1"/>
     </row>
-    <row r="67" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A67" s="2" t="s">
         <v>14</v>
       </c>
@@ -4431,7 +4519,7 @@
       <c r="N67" s="2"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A68" s="2" t="s">
         <v>14</v>
       </c>
@@ -4468,7 +4556,7 @@
       <c r="N68" s="2"/>
       <c r="O68" s="1"/>
     </row>
-    <row r="69" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A69" s="2" t="s">
         <v>14</v>
       </c>
@@ -4505,7 +4593,7 @@
       <c r="N69" s="2"/>
       <c r="O69" s="1"/>
     </row>
-    <row r="70" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A70" s="2" t="s">
         <v>14</v>
       </c>
@@ -4536,13 +4624,26 @@
       <c r="J70" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="1"/>
-    </row>
-    <row r="71" spans="1:15" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K70" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="M70" s="2">
+        <v>100</v>
+      </c>
+      <c r="N70" s="2">
+        <v>80</v>
+      </c>
+      <c r="O70" s="1">
+        <v>100</v>
+      </c>
+      <c r="P70" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A71" s="2" t="s">
         <v>14</v>
       </c>
@@ -4573,13 +4674,26 @@
       <c r="J71" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="1"/>
-    </row>
-    <row r="72" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K71" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="M71" s="2">
+        <v>200</v>
+      </c>
+      <c r="N71" s="2">
+        <v>90</v>
+      </c>
+      <c r="O71" s="1">
+        <v>100</v>
+      </c>
+      <c r="P71" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A72" s="2" t="s">
         <v>14</v>
       </c>
@@ -4610,13 +4724,26 @@
       <c r="J72" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="1"/>
-    </row>
-    <row r="73" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K72" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="M72" s="2">
+        <v>100</v>
+      </c>
+      <c r="N72" s="2">
+        <v>100</v>
+      </c>
+      <c r="O72" s="1">
+        <v>150</v>
+      </c>
+      <c r="P72" s="10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A73" s="2" t="s">
         <v>14</v>
       </c>
@@ -4647,13 +4774,26 @@
       <c r="J73" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="1"/>
-    </row>
-    <row r="74" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K73" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="M73" s="2">
+        <v>300</v>
+      </c>
+      <c r="N73" s="2">
+        <v>120</v>
+      </c>
+      <c r="O73" s="1">
+        <v>100</v>
+      </c>
+      <c r="P73" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A74" s="2" t="s">
         <v>14</v>
       </c>
@@ -4684,11 +4824,24 @@
       <c r="J74" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="1"/>
+      <c r="K74" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="M74" s="2">
+        <v>100</v>
+      </c>
+      <c r="N74" s="2">
+        <v>100</v>
+      </c>
+      <c r="O74" s="1">
+        <v>100</v>
+      </c>
+      <c r="P74" s="10">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/chemical_db.xlsx
+++ b/chemical_db.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HM\Desktop\수질프로그램\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FFFFFD-F50F-4E2D-8BC9-D96A36943E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA3B6C3-D6B4-47CE-B8AB-E1276D76238B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="363">
   <si>
     <t>System</t>
   </si>
@@ -81,9 +81,6 @@
     <t>RO</t>
   </si>
   <si>
-    <t>Main_Ingredient</t>
-  </si>
-  <si>
     <t>Sales_Point</t>
   </si>
   <si>
@@ -102,27 +99,15 @@
     <t>-</t>
   </si>
   <si>
-    <t>Zinc / High Phosphate / High Polymer</t>
-  </si>
-  <si>
     <t>MCO-308AA</t>
   </si>
   <si>
-    <t>[고농축 운전] LSI +2.8 초과(예: +3.0) 시 단독 사용 위험 👉 분산제 추가 투입 및 황산 병행 주입 검토</t>
-  </si>
-  <si>
     <t>MCO-308E</t>
   </si>
   <si>
-    <t>[스케일 주의] 폴리머 미포함 제품 👉 LSI +2.5 이상 상승 시 반드시 분산제 별도 병행 투입 필요</t>
-  </si>
-  <si>
     <t>MCO-308PB</t>
   </si>
   <si>
-    <t>[칼슘 경도] 칼슘 경도가 500ppm 이상일 경우 인산칼슘 스케일 주의 👉 주기적 블로우다운 실시</t>
-  </si>
-  <si>
     <t>MCO-180E</t>
   </si>
   <si>
@@ -180,18 +165,12 @@
     <t>MCO-120C</t>
   </si>
   <si>
-    <t>[스케일] 단독 사용 시 스케일 억제력 부족할 수 있음. 저농축 운전 현장용.</t>
-  </si>
-  <si>
     <t>MCO-452</t>
   </si>
   <si>
     <t>MCZ-921C</t>
   </si>
   <si>
-    <t>Zinc</t>
-  </si>
-  <si>
     <t>MCD-747B</t>
   </si>
   <si>
@@ -255,45 +234,27 @@
     <t>+0.5 ~ +1.5</t>
   </si>
   <si>
-    <t>Zinc / Molybdate / Polymer</t>
-  </si>
-  <si>
-    <t>DBNPA</t>
-  </si>
-  <si>
     <t>DBNPA (속효성 살균제)</t>
   </si>
   <si>
-    <t>[Quick Kill] 투입 후 30분 내 빠른 살균 및 분해. 배출수 환경 영향 최소화.</t>
-  </si>
-  <si>
     <t>MBO-CHZ-7</t>
   </si>
   <si>
     <t>복합 탈산제</t>
   </si>
   <si>
-    <t>[안전] 하이드라진 대체품으로 안전성 우수. 급수 온도 60℃ 이상 유지 권장.</t>
-  </si>
-  <si>
     <t>MBO-CHZ75</t>
   </si>
   <si>
     <t>MBO-1040</t>
   </si>
   <si>
-    <t>[반응] 150℃ 이상 고온에서 산소 제거 반응 속도가 매우 빠름</t>
-  </si>
-  <si>
     <t>MBO-0815</t>
   </si>
   <si>
     <t>복수 처리제</t>
   </si>
   <si>
-    <t>[pH 관리] 응축수(복수) pH 8.5~9.0 유지되도록 주입량 조절 (CO2 중화)</t>
-  </si>
-  <si>
     <t>MBB-1100ODT</t>
   </si>
   <si>
@@ -399,9 +360,6 @@
     <t>유기물/미생물 오염 제거용 알칼리 세정제</t>
   </si>
   <si>
-    <t>[세정] 오일/슬라임 오염 시 계면활성제 효과로 세정력 우수</t>
-  </si>
-  <si>
     <t>MRO-8844</t>
   </si>
   <si>
@@ -411,9 +369,6 @@
     <t>LSI &lt; +2.5</t>
   </si>
   <si>
-    <t>[고경도] 칼슘 경도가 높은 난용성 수질에 적합</t>
-  </si>
-  <si>
     <t>Antiscalant (Standard)</t>
   </si>
   <si>
@@ -426,9 +381,6 @@
     <t>탄산칼슘(CaCO3) 제어 표준형</t>
   </si>
   <si>
-    <t>[표준] 일반적인 수돗물/공업용수 원수 조건에 경제적인 제품</t>
-  </si>
-  <si>
     <t>MRO-2011</t>
   </si>
   <si>
@@ -450,9 +402,6 @@
     <t>황산염(CaSO4, BaSO4) 스케일 억제 탁월</t>
   </si>
   <si>
-    <t>[지하수] 황산이온(SO4) 농도가 높은 지하수 원수에 최적</t>
-  </si>
-  <si>
     <t>MRD-2200AP</t>
   </si>
   <si>
@@ -465,25 +414,6 @@
     <t>MRD-2714A</t>
   </si>
   <si>
-    <t>ATMPS-4Na / NaOH</t>
-  </si>
-  <si>
-    <t>Carbohydrazide(7%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Carbohydrazide(10%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Carbohydrazide / MEA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MEKOR, Morpholine</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>응축수 부식방지 및 방식제(휘발성)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -496,10 +426,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[저압,중압] 저압,중압 보일러의 용존산소 제거 및 금속 부동태화 형성 탁월</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MCD-738</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -524,10 +450,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>높은 농축도 및 Ca 농도 500ppm이상 유지시 추가 적용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Acid Cleaning </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -544,843 +466,926 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Organic Phosphate / Polymer / Azole</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>-1.0 ~ +1.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Organic Phosphate </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>냉각수 주처리제(CTBDR)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PBTC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>고농도 유기인산(100ppm 투입시 T-PO4: 8.4ppm)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>-0.5 ~ +2.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHMP/PBTC/Polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zinc / HEDP / High Polymer / sulfamic Acid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Two 유기 인산염(100ppm 투입시 T-PO4: 4.7ppm)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>비아연계 인산염(100ppm 투입시 T-PO4: 20.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+0.5 ~ +2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산주입형 고농도 인산염 부식방지제(100ppm 투입시 T-PO4: 6.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:19ppm, Zn:2.2ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two 유기 인산염+Azole+폴리머 함유(100ppm 투입시 T-PO4: 4.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-유기인산염계 부식 및 스케일방지제(100ppm 투입시 T-PO4: 4.4ppm, Zn:1 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 6.9ppm,Zn:1 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 13.7ppm,Zn:2 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 8.8ppm,Zn:1.3 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 12.3ppm,Zn:1.8 ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low Phosphate 방류기준(T-P, Zn)기준 제품(100ppm투입시 T-PO4:1.8ppm,Zn: 3ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-P 프로그램(100ppm 투입시 Zn:2.2ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:25.7ppm, Zn:2.2ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:19ppm, Zn:1.8ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 방식, 비아연계 인산염(100ppm 투입시 T-PO4:16ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몰리브데이트 함유: 강력한 부식 억제 (100ppm투입시 T-PO4:3.4ppm,Zn:1.4ppm,Mo:1.5ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아연-인산염계 부식방지제(100ppm투입시 T-Po4: 5.4ppm, Zn: 4ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[아연 관리] 고알칼리 수질에서 Zinc Solubility 저하 주의 👉 pH 8.3~8.5 이하 관리 권장</t>
+  </si>
+  <si>
+    <t>밀폐계 시스템 부식방지제(100ppm 투입시 NO2: 16ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 인산염(방식 우수)(100ppm 투입시 T-PO4: 33ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 인산염, 철부식 탁월(100ppm 투입시 T-PO4:21.5ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유기인산염 단독(100ppm 투입시 T-PO4: 21ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴리인산염 단독(100ppm 투입시 T-PO4: 8.4ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 부식 억제(100ppm 투입시 T-Zn: 9.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철분제거용 스케일분산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황산염(CaSO4, BaSO4) 스케일 억제 탁월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Isothiazoline/질산동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안정화 액상 브롬계 살균제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NaBR/NaOCl/sulfamic Acis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>염소 살균제 pH 8이상 살균력 급감, pH 9수준까지도 살균력 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴리머 단독 제품(Ca염,철염,아연염)스케일 제거 탁월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성능 분산제 (CaCO3,CaPO4,Fe(OH)2,Zn(OH)2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성능 분산제 (CaCO3,CaPO4,Fe(OH)2,Zn(OH)3)</t>
+  </si>
+  <si>
+    <t>고성능 분산제 (CaCO3,CaPO4,Fe(OH)2,Zn(OH)4)</t>
+  </si>
+  <si>
+    <t>고성능 분산제 (CaCO3,CaPO4,SiO2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈산소제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카보하이드라진 7% 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카보하이드라진 10% 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP/아황산나트륨/폴리머/DEHA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복합청관제(탈산소제+청관제+응축수부식방지제)(100ppm 투입시 T-PO4: 3.3ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복합청관제(탈산소제+청관제+응축수부식방지제)(100ppm 투입시 T-PO4: 6.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBB-1100ODT 50% 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Alkaline Cleaning </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순수용 및 고압(KOH) 보일러 청관제(100ppm 투입시 T-PO4: 9.1%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연수용 저압 보일러 청관제(100ppm 투입시 T-PO4: 5.0%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP/KOH/Carbo/MEA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고압 및 농축배수 50배수 Cycle 시스템 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고압 보일러 청관제 및 응축수 부식방지제 (100ppm 투입시 T-PO4: 0.8ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고압 보일러 청관제 및 응축수 부식방지제 (100ppm 투입시 T-PO4: 2.4ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고압 보일러 청관제 및 응축수 강화 방지제 (100ppm 투입시 T-PO4: 4.6ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP , NaOH (Na/PO4= 2.93:1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중,고압 보일러 청관제(100ppm 투입시 T-PO4:5.1ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중,고압 보일러 청관제(100ppm 투입시 T-PO4:6.1ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP , NaOH (Na/PO4= 2.84:1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저압.중압(60kg/cm2 이하)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저압,중압 보일러 청관제(100ppm 투입시 T-PO4:5.1ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cabo./폴리머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐열보일러용 청관제 (Non-PO4) 청관제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저압 보일러 청관제(100ppm 투입시 T-PO4: 3.2ppm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Na/PO4 비율이 2.6~2.85 구간으로 안정화된 인산염 처리/전처리 경도성분 철저히 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이클로 아민 + M.E.A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응축수 부식 방지제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응축수 배관 길이 초반부 효과적/현장 길이가 긴 시스템에 효과 저하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복합 탈산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈산소제+ 응축수 부식방지제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BioOX-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산화성 살균제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ca(Ocl)2 70%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효염소 1ppm 투입시 Ca 및 M-알칼리도(as CaCo3기준) 약 0.7~0.8ppm 상승</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sulfamic acid / NaOH/NaOCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안정화된 염소 살균제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성능 무기 세정제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구연산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구연산/분산제(소량)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄산칼슘(가성비 세정제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH 10~12</t>
+  </si>
+  <si>
+    <t>pH 10~14</t>
+  </si>
+  <si>
+    <t>pH 10~15</t>
+  </si>
+  <si>
+    <t>pH 10~16</t>
+  </si>
+  <si>
+    <t>유기물 오염</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 유기물 오염</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG/ EDTA-4Na/TEA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경제형 알칼리세정제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오염이 심하지 않은 정기적 세정/비용절감</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄산칼슘(CaCO3) 및 황산염 스케일,콜로이드 입자 분산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MRD-3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LSI &lt; +2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄산칼슘외 실리카 전용 분산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antiscalant (Silica)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_LSI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_CaSO4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_SiO2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_BaSO4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_SrSO4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_CaF2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.5~30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200~400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.5~31</t>
+  </si>
+  <si>
+    <t>200~401</t>
+  </si>
+  <si>
+    <t>2.5~32</t>
+  </si>
+  <si>
+    <t>200~402</t>
+  </si>
+  <si>
+    <t>2.5~33</t>
+  </si>
+  <si>
+    <t>200~403</t>
+  </si>
+  <si>
+    <t>2.5~34</t>
+  </si>
+  <si>
+    <t>200~404</t>
+  </si>
+  <si>
+    <t>pH 10~13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[고농축 표준] PBTC와 ATMP 복합제로 스케일 억제력이 우수합니다. ⚠️ 폴리머가 없는 제품이므로, 스케일 위험 시 반드시 분산제(MCD-403D1S)를 병행 투입해야 합니다.</t>
+  </si>
+  <si>
+    <t>[슬러지/스케일] PBTC의 스케일 억제력과 HPMA의 탁월한 이물질 분산력이 조화된 제품입니다. 유속이 느리거나 슬러지 퇴적이 우려되는 설비에 적합합니다.</t>
+  </si>
+  <si>
+    <t>[표준 경제형] HEDP와 아연이 복합된 표준 약품입니다. LSI +2.0 이하의 일반 수질에 적합하며, AR-545 폴리머가 함유되어 기본적인 분산력을 제공합니다.</t>
+  </si>
+  <si>
+    <t>[밸런스 처방] 정인산(방식)과 BENEPOLY 310(스케일/분산)의 균형이 잡힌 제품입니다. 인산칼슘 억제력이 우수하여 다양한 수질에 적용 가능합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[비아연 방식] 아연 없이 정인산과 고농도 BENEPOLY 310을 사용합니다. 아연 배출 규제가 있거나, 알칼리성 수질에서 아연 스케일이 우려될 때 적합합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[방식 강화] 아연과 정인산 함량이 높아 부식 제어에 유리합니다. pH 상승 시 스케일 위험이 있으므로 산 주입과 병행하여 pH를 7.8~8.0으로 유지하십시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[고농축/스케일] PBTC와 ATMP가 주성분이며, 폴리머(2.3%)가 소량 함유됨. 고경도 시 분산제 보강 권장.</t>
+  </si>
+  <si>
+    <t>[무인산 방식] 인산염 없이(Non-P) 아연과 폴리머로만 구성된 방식제입니다. 인산칼슘 위험이 없습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고농도 아연 보강용입니다. 단독 사용 시 스케일 주의. 냉각수 추가 부식 방지제. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HPMA 20% 함유로 진흙, 산화철, 슬러지 분산에 효과적입니다.높은 농축도 및 Ca 농도 500ppm이상 유지시 추가 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBNPA(5%) 기반으로 속효성 살균 효과가 있습니다. 투입 후 30분 내 빠른 살균 및 분해. 배출수 환경 영향 최소화.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[고압/청관제] 카보하이드라자이드(CHZ) 기반의 비독성 산소제거제입니다. 식품/제약 등 고압 증기 설비에 적합합니다.</t>
+  </si>
+  <si>
+    <t>[고압/복합] CHZ(탈산소)와 MEA(pH조정)가 복합되어 급수 라인 부식을 동시에 억제합니다.</t>
+  </si>
+  <si>
+    <t>[고농축 탈산소] 고농도 CHZ(10.4%) 처방으로 용존 산소 제거 능력이 탁월합니다.</t>
+  </si>
+  <si>
+    <t>[전처리 복합] 탈산소제(CHZ)와 중화 아민이 복합되어, 보일러 본체와 응축수 라인을 동시에 보호합니다.</t>
+  </si>
+  <si>
+    <t>[올인원] 탈산소(아황산), 스케일(인산/폴리머), 응축수(DEEA) 처리가 하나로 가능한 복합 청관제입니다.</t>
+  </si>
+  <si>
+    <t>[스케일/부식] 고농도 인산염과 알칼리(KOH)로 스케일을 막고 pH를 유지합니다. (탈산소제 별도 투입 필요),순수 수질 알칼리도 없어서 pH 상향조정하기 위해 알칼리도가 높은 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[표준 청관제] 인산염과 폴리머 기반의 표준형 스케일 방지제입니다.보일러 농축배수 10~15 Cycle 시스템 이용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[복합 관리] 알칼리도 조정과 탈산소, 응축수 처리를 동시에 수행합니다. MBB-1123CHY 3배 농도 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[복합 관리] 알칼리도 조정과 탈산소, 응축수 처리를 동시에 수행합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Na/PO4 비율이 3.0보다 낮으므로, 물이 농축되어도 가성소다가 단독으로 생성안됨.고농도 폴리머(AR-241 8.1%)를 사용하여 칼슘/마그네슘 경도 성분을 강력하게 분산시킵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[알칼리/청관] 높은 알칼리도(NaOH 10%)를 공급하여 보일러수 pH를 안정적으로 유지합니다.저압용 보일러,농축배수 15배수 이상 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2종의 휘발성 아민이 증기와 함께 이동하여, 응축수 배관 전체의 탄산 부식을 방지합니다.응축수 배관 길이 초반부+말단부에 효과적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 아민 복합제로, 응축수 pH가 낮거나 배관 거리가 먼 현장에 강력 추천합니다.MBC-8790제품의 1.5배 농도 제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEKOR(유기 탈산소제)와 모르폴린이 배합되어 고압 보일러의 금속 표면 부동태화에 유리합니다.고압,대형 보일러 시스템 적용(휘발성 처리 프로그램)/응축수 말단 pH 유의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-Phosphate 제품,폐열 보일러용/Blow-down 어려운 시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멤브레인 손상이 적은 안정화된 산화성 살균제입니다. 슬라임 제거에 효과적입니다. 일반적인 RO 시스템 비추천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EDTA와 TEA가 배합되어 멤브레인의 유기물 오염과 미생물 막을 효과적으로 세정합니다.[고경도] 칼슘 경도가 높은 난용성 수질에 적합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 EDTA(15%)를 함유하여 유기물 및 금속 이온 오염을 강력하게 제거합니다.유기오염이 약한곳, 정기적인 RO CIP 약품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[고농축 세정] TEA(35%)와 EDTA의 강력한 킬레이팅 작용으로 심한 유기물 오염을 복원합니다.</t>
+  </si>
+  <si>
+    <t>[최고급 세정] 알칼리 빌더와 킬레이트제가 고농도로 처방된 최상급 알칼리 세정제입니다.</t>
+  </si>
+  <si>
+    <t>[복합 방지제] 인산염과 폴리머(BENEPOLY)가 복합되어 다양한 종류의 스케일과 입자성 물질을 제어합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[고농축 방지제] 고농도 인산염(Total 35% 이상) 처방으로 고회수율 RO 운전에 적합합니다.</t>
+  </si>
+  <si>
+    <t>[실리카 전용] Accumer 5000 폴리머가 함유되어 실리카(Silica) 스케일 억제에 특화된 제품입니다.</t>
+  </si>
+  <si>
+    <t>[표준 방지제] ATMPS 단일 고농축 제제로, 일반적인 탄산칼슘 스케일 제어에 경제적입니다.</t>
+  </si>
+  <si>
+    <t>[분말 세정제] 순수 구연산(98%) 분말입니다. 무기물 스케일(탄산칼슘) 제거용 산성 세정제입니다.</t>
+  </si>
+  <si>
+    <t>[고농축 산성] 구연산 94% 액상으로, 희석하여 사용하는 경제적인 무기물 세정제입니다.</t>
+  </si>
+  <si>
+    <t>[약알칼리 세정] 메타규산염 기반의 순한 알칼리 세정제로, 가벼운 오염 제거나 유지관리용으로 적합합니다.</t>
+  </si>
+  <si>
+    <t>BENEPOLY 310 19.0%</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">[아연 관리] 고알칼리 수질에서 Zinc Solubility 저하 주의 </t>
+      <t>[황산염 특화]</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> DETPMP 함량이 매우 높아 황산칼슘(CaSO4), 황산바륨(BaSO4) 스케일 억제력이 최상급입니다. 회수율을 75% 이상 높게 잡는 현장에 필수입니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[하이브리드 세정]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 산성(구연산, 인산)과 킬레이트(EDTA)가 동시에 작용합니다. 무기물 스케일과 금속 산화물이 혼재된 복합 오염 멤브레인을 한 번에 세정할 때 강력한 효과를 냅니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[액상 산성 세정]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 고농도 구연산 액상에 분산제(HPMA)가 첨가되어, 떨어져 나온 스케일이 다시 달라붙지 않도록(Re-deposition 방지) 돕습니다. 일반 구연산보다 세정 효율이 높습니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>Scale_Inhibitor</t>
+  </si>
+  <si>
+    <t>Closed_System</t>
+  </si>
+  <si>
+    <t>Main_Ingredient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">PBTC / ATMP / BENEPOLY 310 / Tolyltriazole </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">H3PO4/ Zinc Sulf. / BENEPOLY 304  / Tolyltriazole </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">PBTC / ATMP </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PBTC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SHMP / PBTC / HPMA </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HEDP  / Zinc Sulf. / AR-545  / Tolyltriazole </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HEDP  / H3PO4 / Zinc Sulf./ BENEPOLY 310 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HEDP  / H3PO4 / Zinc Sulf. / BENEPOLY 310</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">H3PO4 / BENEPOLY 310 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HEDP  / H3PO4/ Zinc Sulf. / BENEPOLY 310 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HEDP  / H3PO4 / Zinc Sulf. / BENEPOLY 310 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">H3PO4 / Zinc Sulf. / BENEPOLY 310  / Tolyltriazole </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">H3PO4 / Zinc Sulf. / BENEPOLY 310 / Tolyltriazole </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HEDP / H3PO4/ Zinc Sulf. / BENEPOLY 310 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HEDP  / H3PO4 / Zinc Sulf.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TKPP / BENEPOLY 310 / KOH/ H3PO4/ Azole </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc Sulf. / Sod.Molybdate / BENEPOLY 310  / H3PO4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Zinc Sulf. / H3PO4 / BENEPOLY 310 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Sod.Nitrite / Tolyltriazole </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">H3PO4 / SHMP / BENEPOLY 202 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc Chloride(고상) 22.4%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BENEPOLY 310 / Citric Acid </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BENEPOLY 310 / HEDP </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DBNPA </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BENEPOLY 310</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BENEPOLY 310 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCUMER 3100 / PBTC </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carbohydrazide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbohydrazide / MEA </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbohydrazide / Cyclohexylamine / MEA </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TKPP / AR-241  / Sulfite / DEHA </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TKPP  / AR-241  / KOH </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TKPP  / AR-241  / NaOH </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TKPP  / AR-241  / Carbohydrazide  / MEA </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TKPP  / Carbohydrazide  / MEA  / KOH </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SHMP  / AR-241  / NaOH </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclohexylamine  / MEA </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MEKOR  / Morpholine </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구연산 / EDTA / 인산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구연산 / HPMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EDTA-4Na / TEA / PBTC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EDTA-4Na / ATMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEA / EDTA-4Na / ATMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DETPMP/ HEDP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HEDP  / ATMP  / DETPMP  / BENEPOLY 310 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HEDP / ATMP/ DETPMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accumer 5000 / HEDP / PBTC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ATMPS </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[방식 주력] 고농도 정인산과 아연으로 부식을 강력히 억제합니다. 아연 스케일 주의.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[초고농축 전용] 고농도 PBTC로 LSI +3.0의 고알칼리 수질에서도 탄산칼슘을 억제합니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Segoe UI Emoji"/>
         <family val="2"/>
       </rPr>
-      <t>👉</t>
+      <t>🚨</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> pH 8.3~8.5 이하 관리 권장</t>
+      <t xml:space="preserve"> 폴리머 미포함이므로 인산칼슘 방지를 위해 분산제 병행이 필수입니다.</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>비아연계 인산염(100ppm 투입시 T-PO4: 20.6ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zinc / 정인산 / HEDP / Azole/ polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[LSI 관리] LSI +2.5 이상 고부하 운전 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>👉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> 황산 주입 설비 가동 상태 점검 필수</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zinc / 정인산 / HEDP / polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCO-524AA 제품의 2배함량(Azole 없음)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정인산/고농도polymer/황산</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>+0.5 ~ +2.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>산주입형 고농도 인산염 부식방지제(100ppm 투입시 T-PO4: 6.6ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대형플랜트 및 고경도 수질에 적합</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCO-524AA 제품의 1.3배함량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCO-524AA 제품의 1.8배함량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zinc / 정인산 / High Polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고경도 수질 및 농축배수 과부하 시스템 적용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:19ppm, Zn:2.2ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Two 유기 인산염+Azole+폴리머 함유(100ppm 투입시 T-PO4: 4.6ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아연-유기인산염계 부식 및 스케일방지제(100ppm 투입시 T-PO4: 4.4ppm, Zn:1 ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 6.9ppm,Zn:1 ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 13.7ppm,Zn:2 ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 8.8ppm,Zn:1.3 ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아연-인산염계 부식방지제(100ppm투입시 T-PO4: 12.3ppm,Zn:1.8 ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Low Phosphate 방류기준(T-P, Zn)기준 제품(100ppm투입시 T-PO4:1.8ppm,Zn: 3ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Non-P 프로그램(100ppm 투입시 Zn:2.2ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Non-P 냉각수 프로그램 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>👉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> pH 8.3~8.5 이하 관리 권장</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zinc/ Azole/ High Polymer/sulfamic Acid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zinc/ 정인산 / HEDP / Polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:25.7ppm, Zn:2.2ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저농축 및 저경도 수질 추천(철강 플랜트)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Zinc/ 정인산 / HEDP </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>강력한 방식, 저경도 수질 추천(100ppm 투입시 T-PO4:19ppm, Zn:1.8ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저농축 및 저경도 수질 추천(철강 플랜트),직접수 계열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정인산/poly-phosphate/High polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>강력한 방식, 비아연계 인산염(100ppm 투입시 T-PO4:16ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>몰리브데이트 함유: 강력한 부식 억제 (100ppm투입시 T-PO4:3.4ppm,Zn:1.4ppm,Mo:1.5ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉각수 저유속 및 하부부식 효과 탁월</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아연-인산염계 부식방지제(100ppm투입시 T-Po4: 5.4ppm, Zn: 4ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[아연 관리] 고알칼리 수질에서 Zinc Solubility 저하 주의 👉 pH 8.3~8.5 이하 관리 권장</t>
-  </si>
-  <si>
-    <t>Sodium Nitrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>밀폐계 시스템 부식방지제(100ppm 투입시 NO2: 16ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부식성수질, 짧은 체류시간,Ca 500ppm이하 분산제 불필요, 폴리머 주입량: 0.5&lt;(UFPO4-FPO4)&lt;2.0ppm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>체류시간이 길고, 농축배수가 높은 냉각시스템 적용,폴리머 주입량: 0.5&lt;(UFPO4-FPO4)&lt;2.0ppm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[pH 관리] pH 8.3 이상 상승 시 아연(Zinc) 스케일 발생 위험 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>👉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> 산 주입으로 pH 7.8~8.0 유지 필수</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>밀폐계 시스템(450~550ppm NO2)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정인산/polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고농도 인산염(방식 우수)(100ppm 투입시 T-PO4: 33ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저농축 및 인산염 단독 처리(비용절감)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정인산/SHM/polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고농도 인산염, 철부식 탁월(100ppm 투입시 T-PO4:21.5ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철부식 산화물 및 저농축 시스템(철강 플랜트)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TKPP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHMP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유기인산염 단독(100ppm 투입시 T-PO4: 21ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>폴리인산염 단독(100ppm 투입시 T-PO4: 8.4ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>강력한 부식 억제(100ppm 투입시 T-Zn: 9.6ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[방식 전용] 냉각수 추가 부식 방지제. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Polymer / 구연산</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철분제거용 스케일분산제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철강 분산제(OG분산제용)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HEDP/polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>황산염(CaSO4, BaSO4) 스케일 억제 탁월</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>농축기 시스템 특화 분산제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Isothiazoline/질산동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안정화 액상 브롬계 살균제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NaBR/NaOCl/sulfamic Acis</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>염소 살균제 pH 8이상 살균력 급감, pH 9수준까지도 살균력 유지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Polymer </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>폴리머 단독 제품(Ca염,철염,아연염)스케일 제거 탁월</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고성능 분산제 (CaCO3,CaPO4,Fe(OH)2,Zn(OH)2)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고성능 분산제 (CaCO3,CaPO4,Fe(OH)2,Zn(OH)3)</t>
-  </si>
-  <si>
-    <t>MCD-4035 50%제품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고성능 분산제 (CaCO3,CaPO4,Fe(OH)2,Zn(OH)4)</t>
-  </si>
-  <si>
-    <t>MCD-4035 50%제품, 안료 첨가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PBTC/ polymer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고성능 분산제 (CaCO3,CaPO4,SiO2)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실리카 전용 및 칼슘염 분산제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탈산소제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카보하이드라진 7% 제품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카보하이드라진 10% 제품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Neutralizing Amine+ Carbohydrazide(8%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TKPP/아황산나트륨/폴리머/DEHA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[종합] 소형,중형 수관보일러 전용. 약품 하나로 스케일/부식/용존산소 동시 제어.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>복합청관제(탈산소제+청관제+응축수부식방지제)(100ppm 투입시 T-PO4: 3.3ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>복합청관제(탈산소제+청관제+응축수부식방지제)(100ppm 투입시 T-PO4: 6.6ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MBB-1100ODT 50% 제품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Alkaline Cleaning </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TKPP/KOH/폴리머</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>순수용 및 고압(KOH) 보일러 청관제(100ppm 투입시 T-PO4: 9.1%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>순수 수질 알칼리도 없어서 pH 상향조정하기 위해 알칼리도가 높은 제품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TKPP/NaOH/폴리머</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연수용 저압 보일러 청관제(100ppm 투입시 T-PO4: 5.0%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보일러 농축배수 10~15 Cycle 시스템 이용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TKPP/KOH/Carbo/MEA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고압 및 농축배수 50배수 Cycle 시스템 적용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고압 보일러 청관제 및 응축수 부식방지제 (100ppm 투입시 T-PO4: 0.8ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고압 보일러 청관제 및 응축수 부식방지제 (100ppm 투입시 T-PO4: 2.4ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MBB-1123CHY 3배 농도 제품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TKPP/KOH/Carbo/MEA/폴리머</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고압 보일러 청관제 및 응축수 강화 방지제 (100ppm 투입시 T-PO4: 4.6ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>급수 수질 안정화 시스템+ 응축수 스팀 라인 보호에 초점/분산제가 없으므로 경도성분 유입시 스케일 유발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHMP , NaOH (Na/PO4= 2.8:1)/폴리머</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHMP , NaOH (Na/PO4= 2.93:1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>중,고압 보일러 청관제(100ppm 투입시 T-PO4:5.1ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>중,고압 보일러 청관제(100ppm 투입시 T-PO4:6.1ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHMP , NaOH (Na/PO4= 2.84:1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Na/PO4 비율이 3.0보다 낮으므로, 물이 농축되어도 가성소다가 단독으로 생성안됨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저압.중압(60kg/cm2 이하)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저압,중압 보일러 청관제(100ppm 투입시 T-PO4:5.1ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cabo./폴리머</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>폐열보일러용 청관제 (Non-PO4) 청관제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>폐열 보일러용/Blow-down 어려운 시스템</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저압 보일러 청관제(100ppm 투입시 T-PO4: 3.2ppm)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Na/PO4 비율이 2.6~2.85 구간으로 안정화된 인산염 처리/전처리 경도성분 철저히 관리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHMP,가성소다/폴리머</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저압용 보일러,농축배수 15배수 이상 적용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사이클로 아민 + M.E.A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>응축수 부식 방지제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>응축수 배관 길이 초반부+말단부에 효과적</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MBC-8790제품의 1.5배 농도 제품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>응축수 배관 길이 초반부 효과적/현장 길이가 긴 시스템에 효과 저하</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>복합 탈산제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탈산소제+ 응축수 부식방지제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고압,대형 보일러 시스템 적용(휘발성 처리 프로그램)/응축수 말단 pH 유의</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BioOX-100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>산화성 살균제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ca(Ocl)2 70%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유효염소 1ppm 투입시 Ca 및 M-알칼리도(as CaCo3기준) 약 0.7~0.8ppm 상승</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sulfamic acid / NaOH/NaOCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안정화된 염소 살균제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설파믹산 결합염소, 일반적인 RO 시스템 비추천</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구연산/인산/글리코산/킬레이트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고성능 무기 세정제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탄산칼슘외 철분,망간,실리카등 난용성 오염물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구연산</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구연산/분산제(소량)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구연산/스케일방지제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RO시스템 표준 세정제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탄산칼슘(가성비 세정제)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>황산칼슘 및 실리카 제거 어려움</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[세정] 단순 산 세정제, 40℃ 순환 세정 시 세정 효율 극대화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PBTC / EDTA-4Na/TEA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pH 10~12</t>
-  </si>
-  <si>
-    <t>pH 10~13</t>
-  </si>
-  <si>
-    <t>pH 10~14</t>
-  </si>
-  <si>
-    <t>pH 10~15</t>
-  </si>
-  <si>
-    <t>pH 10~16</t>
-  </si>
-  <si>
-    <t>유기물 오염</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고농도 유기물 오염</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PG/ EDTA-4Na/TEA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유기오염이 약한곳, 정기적인 RO CIP 약품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유기오염 및 Fe,Mn 오염도가 심한곳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유기오염 및 Fe,Mn 오염도가 매우 심한곳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경제형 알칼리세정제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오염이 심하지 않은 정기적 세정/비용절감</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATMP / DETPMP/HEDP/폴리머</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATMP / DETPMP/HEDP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DETPMP / HEDP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탄산칼슘(CaCO3) 및 황산염 스케일,콜로이드 입자 분산</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[고회수율]  LSI +2.8 고부하 운전 가능</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MRD-3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LSI &lt; +2.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HEDP/A-5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탄산칼슘외 실리카 전용 분산제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실리카전용 분산제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Antiscalant (Silica)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max_LSI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max_CaSO4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max_SiO2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max_BaSO4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max_SrSO4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max_CaF2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.5~30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200~400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.5~31</t>
-  </si>
-  <si>
-    <t>200~401</t>
-  </si>
-  <si>
-    <t>2.5~32</t>
-  </si>
-  <si>
-    <t>200~402</t>
-  </si>
-  <si>
-    <t>2.5~33</t>
-  </si>
-  <si>
-    <t>200~403</t>
-  </si>
-  <si>
-    <t>2.5~34</t>
-  </si>
-  <si>
-    <t>200~404</t>
+    <t>[강력 방식] 고농도 아연과 정인산으로 부식을 잡고, 고성능 분산제로 스케일을 막습니다. 아연 농도가 높아 pH 8.3 이하 관리가 요구됩니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[표준 복합] 아연과 정인산, BENEPOLY 310이 복합된 표준 제품입니다. 부식과 스케일, 슬러지를 동시에 제어합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[저경도/저인산] 인산염을 최소화하고 고농도 아연과 폴리머로 부식을 잡는 특수 처방입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[고농도 올인원] 정인산과 HEDP가 고농도로 처방된 강력한 제품입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[방식 주력] 정인산 위주의 처방입니다. 폴리머가 없으므로 분산제 병행이 필요합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[알칼리성 복합제] TKPP와 고농도 폴리머가 배합되어 스케일 분산력이 탁월합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[최고급 복합제] 아연과 몰리브덴의 시너지로 국부 부식(Pitting)을 완벽히 차단합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[밀폐계/초기세정] 아질산나트륨 액상이 60% 함유된 고농도 제품입니다. 배관 부식을 강력 억제합니다. 권장 투입량 밀폐계 시스템(450~550ppm NO2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 인산이 함유되어 pH를 낮추면서 스케일을 제어합니다. 저농축 및 인산염 단독 처리(비용절감)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정인산과 중합인산이 복합되어 부식 억제력이 우수합니다. 철부식 산화물 및 저농축 시스템(철강 플랜트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKPP 단일 제제로, 온수 계통이나 초기 방식 피막 형성에 유리합니다. 단독 사용 시 스케일 억제력 부족할 수 있음. 저농축 운전 현장용.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMP 단일 제제입니다. 부식 억제용으로 사용됩니다. 단독 사용 시 스케일 억제력 부족할 수 있음. 저농축 운전 현장용.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴리머와 구연산이 복합되어 스케일 분산과 약한 세정 효과를 냅니다.철강 분산제(OG분산제용)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고농도 폴리머와 HEDP가 결합되어 스케일 억제력을 강력 보강합니다.농축기 시스템 특화 분산제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BENEPOLY 310 기반의 표준 스케일 분산제입니다.MCD-4035 50%제품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BENEPOLY 310기반의 표준 스케일 분산제입니다. 안료 첨가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACCUMER 3100기반으로 실리카전용 및 탄산칼슘 결정 성장을 억제합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1412,14 +1417,32 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Segoe UI Emoji"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1505,7 +1528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1522,6 +1545,14 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1530,12 +1561,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1847,10 +1872,10 @@
     <col min="4" max="4" width="24.33203125" customWidth="1"/>
     <col min="5" max="5" width="9.1640625" customWidth="1"/>
     <col min="6" max="6" width="16.08203125" customWidth="1"/>
-    <col min="7" max="7" width="21.4140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="39.4140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="24" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="21.4140625" customWidth="1"/>
+    <col min="8" max="8" width="34.25" customWidth="1"/>
+    <col min="9" max="9" width="33.6640625" customWidth="1"/>
+    <col min="10" max="10" width="75.33203125" customWidth="1"/>
     <col min="12" max="12" width="11.25" customWidth="1"/>
     <col min="14" max="14" width="11.08203125" customWidth="1"/>
     <col min="15" max="15" width="10.33203125" customWidth="1"/>
@@ -1879,47 +1904,47 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>337</v>
+        <v>232</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>338</v>
+        <v>233</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>339</v>
+        <v>234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>340</v>
+        <v>235</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>341</v>
+        <v>236</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>342</v>
+        <v>237</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="E2" s="2">
         <v>100</v>
@@ -1928,20 +1953,22 @@
         <v>7</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>22</v>
+        <v>139</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>295</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+        <v>146</v>
+      </c>
+      <c r="J2" t="s">
+        <v>344</v>
+      </c>
+      <c r="K2" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
       <c r="N2" s="2"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -1953,13 +1980,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -1968,38 +1995,40 @@
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>163</v>
+        <v>62</v>
+      </c>
+      <c r="H3" t="s">
+        <v>294</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+        <v>147</v>
+      </c>
+      <c r="J3" t="s">
+        <v>255</v>
+      </c>
+      <c r="K3" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
       <c r="N3" s="2"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
@@ -2008,18 +2037,20 @@
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>165</v>
+        <v>63</v>
+      </c>
+      <c r="H4" t="s">
+        <v>296</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="J4" t="s">
+        <v>249</v>
+      </c>
+      <c r="K4" s="2">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -2028,18 +2059,18 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2">
         <v>100</v>
@@ -2048,18 +2079,20 @@
         <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>167</v>
+        <v>63</v>
+      </c>
+      <c r="H5" t="s">
+        <v>297</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="J5" t="s">
+        <v>345</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -2068,18 +2101,18 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2">
         <v>60</v>
@@ -2087,19 +2120,21 @@
       <c r="F6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>170</v>
+      <c r="G6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" t="s">
+        <v>298</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K6" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="J6" t="s">
+        <v>250</v>
+      </c>
+      <c r="K6" s="2">
+        <v>2.5</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -2113,13 +2148,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
@@ -2128,18 +2163,20 @@
         <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>171</v>
+        <v>61</v>
+      </c>
+      <c r="H7" t="s">
+        <v>299</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K7" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="J7" t="s">
+        <v>251</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -2148,18 +2185,18 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2">
         <v>100</v>
@@ -2168,18 +2205,20 @@
         <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>175</v>
+        <v>61</v>
+      </c>
+      <c r="H8" t="s">
+        <v>300</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="J8" t="s">
+        <v>252</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1.5</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -2188,18 +2227,18 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2">
         <v>100</v>
@@ -2208,18 +2247,20 @@
         <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>177</v>
+        <v>61</v>
+      </c>
+      <c r="H9" t="s">
+        <v>301</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="J9" t="s">
+        <v>346</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1.5</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -2228,18 +2269,18 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2">
         <v>100</v>
@@ -2248,18 +2289,20 @@
         <v>7</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>179</v>
+        <v>144</v>
+      </c>
+      <c r="H10" t="s">
+        <v>302</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="J10" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1.5</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -2268,18 +2311,18 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2">
         <v>100</v>
@@ -2288,18 +2331,20 @@
         <v>7</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>175</v>
+        <v>61</v>
+      </c>
+      <c r="H11" t="s">
+        <v>303</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K11" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="J11" t="s">
+        <v>347</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1.5</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -2313,13 +2358,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2">
         <v>100</v>
@@ -2328,18 +2373,20 @@
         <v>7</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>175</v>
+        <v>61</v>
+      </c>
+      <c r="H12" t="s">
+        <v>304</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="K12" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="J12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1.5</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -2353,13 +2400,13 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" s="2">
         <v>100</v>
@@ -2368,18 +2415,20 @@
         <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>185</v>
+        <v>61</v>
+      </c>
+      <c r="H13" t="s">
+        <v>305</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K13" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="J13" t="s">
+        <v>348</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1.2</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2388,18 +2437,18 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:18" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2">
         <v>100</v>
@@ -2408,18 +2457,20 @@
         <v>7</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>197</v>
+        <v>61</v>
+      </c>
+      <c r="H14" t="s">
+        <v>306</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K14" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="J14" t="s">
+        <v>256</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1.2</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2428,18 +2479,18 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E15" s="2">
         <v>100</v>
@@ -2448,18 +2499,20 @@
         <v>7</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>198</v>
+        <v>139</v>
+      </c>
+      <c r="H15" t="s">
+        <v>307</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K15" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="J15" t="s">
+        <v>349</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2.5</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -2468,18 +2521,18 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" s="2">
         <v>100</v>
@@ -2488,18 +2541,20 @@
         <v>7</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>201</v>
+        <v>61</v>
+      </c>
+      <c r="H16" t="s">
+        <v>308</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K16" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="J16" t="s">
+        <v>350</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -2508,18 +2563,18 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="2">
         <v>100</v>
@@ -2528,18 +2583,20 @@
         <v>7</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>204</v>
+        <v>64</v>
+      </c>
+      <c r="H17" t="s">
+        <v>309</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K17" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="J17" t="s">
+        <v>351</v>
+      </c>
+      <c r="K17" s="2">
+        <v>2</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -2553,13 +2610,13 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" s="2">
         <v>100</v>
@@ -2568,18 +2625,20 @@
         <v>7</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>73</v>
+        <v>61</v>
+      </c>
+      <c r="H18" t="s">
+        <v>310</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="K18" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="J18" t="s">
+        <v>352</v>
+      </c>
+      <c r="K18" s="2">
+        <v>2</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -2588,18 +2647,18 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" s="2">
         <v>100</v>
@@ -2608,16 +2667,16 @@
         <v>7</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>185</v>
+        <v>61</v>
+      </c>
+      <c r="H19" t="s">
+        <v>311</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -2628,18 +2687,18 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>18</v>
+      <c r="B20" t="s">
+        <v>292</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E20" s="2">
         <v>100</v>
@@ -2648,16 +2707,16 @@
         <v>7</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>210</v>
+        <v>65</v>
+      </c>
+      <c r="H20" t="s">
+        <v>312</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>215</v>
+        <v>353</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -2668,18 +2727,18 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="2">
         <v>100</v>
@@ -2688,16 +2747,16 @@
         <v>7</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>216</v>
+        <v>139</v>
+      </c>
+      <c r="H21" t="s">
+        <v>302</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>218</v>
+        <v>354</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -2708,18 +2767,18 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" s="2">
         <v>100</v>
@@ -2728,16 +2787,16 @@
         <v>7</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>219</v>
+        <v>65</v>
+      </c>
+      <c r="H22" t="s">
+        <v>313</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>221</v>
+        <v>355</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -2748,18 +2807,18 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" s="2">
         <v>100</v>
@@ -2768,16 +2827,16 @@
         <v>7</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>222</v>
+        <v>65</v>
+      </c>
+      <c r="H23" t="s">
+        <v>314</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>356</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -2788,18 +2847,18 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
     </row>
-    <row r="24" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" s="2">
         <v>100</v>
@@ -2808,16 +2867,16 @@
         <v>7</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>223</v>
+        <v>63</v>
+      </c>
+      <c r="H24" t="s">
+        <v>315</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>224</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>357</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -2828,18 +2887,18 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" s="2">
         <v>100</v>
@@ -2848,16 +2907,16 @@
         <v>7</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
+      </c>
+      <c r="H25" t="s">
+        <v>316</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>226</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
@@ -2876,10 +2935,10 @@
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="E26" s="2">
         <v>50</v>
@@ -2889,17 +2948,17 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="8"/>
+        <v>136</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="12"/>
       <c r="N26" s="2"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -2914,10 +2973,10 @@
         <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E27" s="2">
         <v>50</v>
@@ -2926,16 +2985,16 @@
         <v>7</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>158</v>
+        <v>258</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
@@ -2954,10 +3013,10 @@
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2">
         <v>30</v>
@@ -2966,16 +3025,16 @@
         <v>7</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>228</v>
+        <v>20</v>
+      </c>
+      <c r="H28" t="s">
+        <v>317</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>230</v>
+        <v>358</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -2994,10 +3053,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E29" s="2">
         <v>30</v>
@@ -3006,16 +3065,16 @@
         <v>7</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>231</v>
+        <v>20</v>
+      </c>
+      <c r="H29" t="s">
+        <v>318</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>233</v>
+        <v>359</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -3034,10 +3093,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>295</v>
+        <v>208</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="E30" s="2">
         <v>50</v>
@@ -3046,16 +3105,16 @@
         <v>7</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>297</v>
+        <v>210</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>298</v>
+        <v>211</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -3074,10 +3133,10 @@
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E31" s="2">
         <v>50</v>
@@ -3086,16 +3145,16 @@
         <v>7</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
@@ -3114,10 +3173,10 @@
         <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E32" s="2">
         <v>50</v>
@@ -3126,16 +3185,16 @@
         <v>7</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
@@ -3154,10 +3213,10 @@
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E33" s="2">
         <v>50</v>
@@ -3166,16 +3225,16 @@
         <v>7</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>74</v>
+        <v>20</v>
+      </c>
+      <c r="H33" t="s">
+        <v>319</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>76</v>
+        <v>259</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
@@ -3194,10 +3253,10 @@
         <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E34" s="2">
         <v>50</v>
@@ -3206,16 +3265,16 @@
         <v>7</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
@@ -3226,7 +3285,7 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" s="2" t="s">
         <v>7</v>
       </c>
@@ -3234,10 +3293,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E35" s="2">
         <v>30</v>
@@ -3246,16 +3305,16 @@
         <v>7</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>238</v>
+        <v>20</v>
+      </c>
+      <c r="H35" t="s">
+        <v>320</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -3266,7 +3325,7 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" s="2" t="s">
         <v>7</v>
       </c>
@@ -3274,10 +3333,10 @@
         <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E36" s="2">
         <v>30</v>
@@ -3286,16 +3345,16 @@
         <v>7</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>238</v>
+        <v>20</v>
+      </c>
+      <c r="H36" t="s">
+        <v>321</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>242</v>
+        <v>360</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -3306,7 +3365,7 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37" s="2" t="s">
         <v>7</v>
       </c>
@@ -3314,10 +3373,10 @@
         <v>8</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E37" s="2">
         <v>30</v>
@@ -3326,16 +3385,16 @@
         <v>7</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>238</v>
+        <v>20</v>
+      </c>
+      <c r="H37" t="s">
+        <v>287</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>243</v>
+        <v>176</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>244</v>
+        <v>361</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
@@ -3354,10 +3413,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E38" s="2">
         <v>30</v>
@@ -3366,16 +3425,16 @@
         <v>7</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>245</v>
+        <v>20</v>
+      </c>
+      <c r="H38" t="s">
+        <v>322</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>246</v>
+        <v>177</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>247</v>
+        <v>362</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -3394,10 +3453,10 @@
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="E39" s="2">
         <v>50</v>
@@ -3406,16 +3465,16 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>144</v>
+        <v>20</v>
+      </c>
+      <c r="H39" t="s">
+        <v>323</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>79</v>
+        <v>179</v>
+      </c>
+      <c r="J39" t="s">
+        <v>260</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
@@ -3434,10 +3493,10 @@
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E40" s="2">
         <v>50</v>
@@ -3446,16 +3505,16 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>146</v>
+        <v>20</v>
+      </c>
+      <c r="H40" t="s">
+        <v>324</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>151</v>
+        <v>128</v>
+      </c>
+      <c r="J40" t="s">
+        <v>261</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -3474,10 +3533,10 @@
         <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="E41" s="2">
         <v>30</v>
@@ -3486,16 +3545,16 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>145</v>
+        <v>20</v>
+      </c>
+      <c r="H41" t="s">
+        <v>323</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>82</v>
+        <v>180</v>
+      </c>
+      <c r="J41" t="s">
+        <v>262</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -3514,10 +3573,10 @@
         <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E42" s="2">
         <v>30</v>
@@ -3526,16 +3585,16 @@
         <v>13</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>251</v>
+        <v>20</v>
+      </c>
+      <c r="H42" t="s">
+        <v>325</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>85</v>
+        <v>126</v>
+      </c>
+      <c r="J42" t="s">
+        <v>263</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
@@ -3546,18 +3605,18 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:18" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>12</v>
+      <c r="B43" t="s">
+        <v>291</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E43" s="2">
         <v>25</v>
@@ -3566,16 +3625,16 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>252</v>
+        <v>20</v>
+      </c>
+      <c r="H43" t="s">
+        <v>326</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>253</v>
+        <v>183</v>
+      </c>
+      <c r="J43" t="s">
+        <v>264</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
@@ -3586,18 +3645,18 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A44" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>12</v>
+      <c r="B44" t="s">
+        <v>291</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E44" s="2">
         <v>50</v>
@@ -3606,16 +3665,16 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>252</v>
+        <v>181</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>254</v>
+        <v>182</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>256</v>
+        <v>184</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
@@ -3626,18 +3685,18 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A45" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>12</v>
+      <c r="B45" t="s">
+        <v>291</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2">
         <v>20</v>
@@ -3646,16 +3705,16 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>258</v>
+        <v>20</v>
+      </c>
+      <c r="H45" t="s">
+        <v>327</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
@@ -3666,18 +3725,18 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>12</v>
+      <c r="B46" t="s">
+        <v>291</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2">
         <v>20</v>
@@ -3686,16 +3745,16 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>261</v>
+        <v>20</v>
+      </c>
+      <c r="H46" t="s">
+        <v>328</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
@@ -3706,18 +3765,18 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
     </row>
-    <row r="47" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>12</v>
+      <c r="B47" t="s">
+        <v>291</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2">
         <v>20</v>
@@ -3726,16 +3785,16 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>269</v>
+        <v>20</v>
+      </c>
+      <c r="H47" t="s">
+        <v>329</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
@@ -3746,18 +3805,18 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A48" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>12</v>
+      <c r="B48" t="s">
+        <v>291</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2">
         <v>20</v>
@@ -3766,16 +3825,16 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>269</v>
+        <v>20</v>
+      </c>
+      <c r="H48" t="s">
+        <v>330</v>
       </c>
       <c r="I48" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
@@ -3786,18 +3845,18 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A49" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>12</v>
+      <c r="B49" t="s">
+        <v>291</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2">
         <v>20</v>
@@ -3806,16 +3865,16 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
@@ -3826,18 +3885,18 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
     </row>
-    <row r="50" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A50" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>12</v>
+      <c r="B50" t="s">
+        <v>291</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2">
         <v>20</v>
@@ -3846,16 +3905,16 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>272</v>
+        <v>20</v>
+      </c>
+      <c r="H50" t="s">
+        <v>331</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>274</v>
+        <v>194</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
@@ -3866,18 +3925,18 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A51" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>12</v>
+      <c r="B51" t="s">
+        <v>291</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2">
         <v>20</v>
@@ -3886,16 +3945,16 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>276</v>
+        <v>196</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>275</v>
+        <v>195</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>284</v>
+        <v>202</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
@@ -3906,18 +3965,18 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A52" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>12</v>
+      <c r="B52" t="s">
+        <v>291</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2">
         <v>20</v>
@@ -3926,16 +3985,16 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>273</v>
+        <v>193</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>279</v>
+        <v>198</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>278</v>
+        <v>197</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
@@ -3946,18 +4005,18 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:18" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A53" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>12</v>
+      <c r="B53" t="s">
+        <v>291</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E53" s="2">
         <v>20</v>
@@ -3966,16 +4025,16 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>285</v>
+        <v>20</v>
+      </c>
+      <c r="H53" t="s">
+        <v>331</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>283</v>
+        <v>201</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
@@ -3990,14 +4049,14 @@
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>12</v>
+      <c r="B54" t="s">
+        <v>291</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E54" s="2">
         <v>30</v>
@@ -4006,16 +4065,16 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>280</v>
+        <v>199</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
@@ -4034,10 +4093,10 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E55" s="2">
         <v>30</v>
@@ -4046,16 +4105,16 @@
         <v>13</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>287</v>
+        <v>20</v>
+      </c>
+      <c r="H55" t="s">
+        <v>332</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>288</v>
+        <v>204</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
@@ -4074,10 +4133,10 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E56" s="2">
         <v>30</v>
@@ -4086,16 +4145,16 @@
         <v>13</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>287</v>
+        <v>20</v>
+      </c>
+      <c r="H56" t="s">
+        <v>332</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>288</v>
+        <v>204</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
@@ -4114,10 +4173,10 @@
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E57" s="2">
         <v>30</v>
@@ -4126,16 +4185,16 @@
         <v>13</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>287</v>
+        <v>203</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>288</v>
+        <v>204</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>291</v>
+        <v>205</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
@@ -4154,10 +4213,10 @@
         <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>292</v>
+        <v>206</v>
       </c>
       <c r="E58" s="2">
         <v>50</v>
@@ -4166,16 +4225,16 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>147</v>
+        <v>20</v>
+      </c>
+      <c r="H58" t="s">
+        <v>333</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>293</v>
+        <v>207</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
@@ -4191,31 +4250,31 @@
         <v>14</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E59" s="2">
         <v>50</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>299</v>
+        <v>212</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
@@ -4228,31 +4287,31 @@
         <v>14</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E60" s="5">
         <v>0.05</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>302</v>
+        <v>98</v>
+      </c>
+      <c r="H60" t="s">
+        <v>334</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>304</v>
+        <v>214</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>289</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
@@ -4265,31 +4324,31 @@
         <v>14</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E61" s="5">
         <v>0.05</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>306</v>
+        <v>216</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>310</v>
+        <v>217</v>
+      </c>
+      <c r="J61" t="s">
+        <v>284</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
@@ -4302,31 +4361,31 @@
         <v>14</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E62" s="5">
         <v>0.05</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>307</v>
+        <v>98</v>
+      </c>
+      <c r="H62" t="s">
+        <v>335</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>308</v>
+        <v>99</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>290</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
@@ -4339,31 +4398,31 @@
         <v>14</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E63" s="5">
         <v>0.05</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>305</v>
+        <v>215</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>311</v>
+        <v>217</v>
+      </c>
+      <c r="J63" t="s">
+        <v>285</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
@@ -4376,31 +4435,31 @@
         <v>14</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E64" s="5">
         <v>0.05</v>
       </c>
       <c r="F64" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I64" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>121</v>
+      <c r="J64" t="s">
+        <v>286</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
@@ -4413,31 +4472,31 @@
         <v>14</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E65" s="5">
         <v>0.05</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>312</v>
+        <v>218</v>
+      </c>
+      <c r="H65" t="s">
+        <v>336</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>318</v>
+        <v>222</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
@@ -4450,31 +4509,31 @@
         <v>14</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E66" s="5">
         <v>0.05</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>312</v>
+        <v>248</v>
+      </c>
+      <c r="H66" t="s">
+        <v>337</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>318</v>
+        <v>222</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
@@ -4487,31 +4546,31 @@
         <v>14</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E67" s="5">
         <v>0.05</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>320</v>
+        <v>219</v>
+      </c>
+      <c r="H67" t="s">
+        <v>338</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>322</v>
+        <v>223</v>
+      </c>
+      <c r="J67" t="s">
+        <v>278</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
@@ -4524,31 +4583,31 @@
         <v>14</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E68" s="5">
         <v>0.05</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>316</v>
+        <v>220</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>323</v>
+        <v>223</v>
+      </c>
+      <c r="J68" t="s">
+        <v>279</v>
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
@@ -4561,31 +4620,31 @@
         <v>14</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E69" s="5">
         <v>0.05</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>317</v>
+        <v>221</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>324</v>
+        <v>225</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>325</v>
+        <v>226</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
@@ -4598,48 +4657,48 @@
         <v>14</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>328</v>
+        <v>110</v>
+      </c>
+      <c r="H70" t="s">
+        <v>339</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>138</v>
+        <v>121</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>288</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>343</v>
+        <v>238</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>344</v>
+        <v>239</v>
       </c>
       <c r="M70" s="2">
         <v>100</v>
       </c>
       <c r="N70" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="O70" s="1">
         <v>100</v>
       </c>
-      <c r="P70" s="10">
+      <c r="P70" s="7">
         <v>100</v>
       </c>
     </row>
@@ -4648,37 +4707,37 @@
         <v>14</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>326</v>
+        <v>123</v>
+      </c>
+      <c r="H71" t="s">
+        <v>340</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>329</v>
+        <v>227</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>345</v>
+        <v>240</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>346</v>
+        <v>241</v>
       </c>
       <c r="M71" s="2">
         <v>200</v>
@@ -4689,7 +4748,7 @@
       <c r="O71" s="1">
         <v>100</v>
       </c>
-      <c r="P71" s="10">
+      <c r="P71" s="7">
         <v>100</v>
       </c>
     </row>
@@ -4698,37 +4757,37 @@
         <v>14</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>327</v>
+        <v>113</v>
+      </c>
+      <c r="H72" t="s">
+        <v>341</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>130</v>
+        <v>114</v>
+      </c>
+      <c r="J72" t="s">
+        <v>281</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>348</v>
+        <v>243</v>
       </c>
       <c r="M72" s="2">
         <v>100</v>
@@ -4739,7 +4798,7 @@
       <c r="O72" s="1">
         <v>150</v>
       </c>
-      <c r="P72" s="10">
+      <c r="P72" s="7">
         <v>200</v>
       </c>
     </row>
@@ -4748,37 +4807,37 @@
         <v>14</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>336</v>
+        <v>231</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>331</v>
+        <v>228</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E73" s="2">
         <v>6</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>333</v>
+        <v>229</v>
+      </c>
+      <c r="H73" t="s">
+        <v>342</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>335</v>
+        <v>230</v>
+      </c>
+      <c r="J73" t="s">
+        <v>282</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>349</v>
+        <v>244</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>350</v>
+        <v>245</v>
       </c>
       <c r="M73" s="2">
         <v>300</v>
@@ -4789,7 +4848,7 @@
       <c r="O73" s="1">
         <v>100</v>
       </c>
-      <c r="P73" s="10">
+      <c r="P73" s="7">
         <v>100</v>
       </c>
     </row>
@@ -4798,37 +4857,37 @@
         <v>14</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>143</v>
+        <v>113</v>
+      </c>
+      <c r="H74" t="s">
+        <v>343</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>130</v>
+        <v>114</v>
+      </c>
+      <c r="J74" t="s">
+        <v>283</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>351</v>
+        <v>246</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>352</v>
+        <v>247</v>
       </c>
       <c r="M74" s="2">
         <v>100</v>
@@ -4839,7 +4898,7 @@
       <c r="O74" s="1">
         <v>100</v>
       </c>
-      <c r="P74" s="10">
+      <c r="P74" s="7">
         <v>100</v>
       </c>
     </row>
@@ -4849,6 +4908,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>